--- a/CGB_HVT_198_bespoke.xlsx
+++ b/CGB_HVT_198_bespoke.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="HVT 1-198" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Links &amp; audit" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HVT 1-198" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Voice audit" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HVT 1-198'!$A$1:$N$199</definedName>
@@ -442,13 +442,13 @@
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="100" customWidth="1" min="11" max="11"/>
+    <col width="104" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
@@ -497,7 +497,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Site link used</t>
+          <t>Site link</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Hi Tim. NGPF owns 9-12 and does it better than anyone. I wrote the K-5 on-ramp: a picture book where a kid runs one real purchase, ad to register, sales tax and all. Genuine question rather than a pitch: do you see elementary as in scope for NGPF, or a gap someone else has to fill? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Tim — NGPF owns 9-12 and does it better than anyone. I wrote the K-5 on-ramp: a picture book where a kid runs one real purchase, ad to register, sales tax and all. Genuine question rather than a pitch — do you see elementary as in scope for NGPF, or a gap somebody else has to fill? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -615,11 +615,11 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Joel, I built a free K-5 toolkit against the National Standards: four 45-minute lesson plans, a pre/post assessment with answer key, and a 23-row standards crosswalk. All ungated, no email capture. I'd like to submit it to the Clearinghouse. Let me know and it ships. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Joel — no login, no email capture, no funnel. Four 45-minute lesson plans, a pre/post assessment with the answer key, and a 23-row crosswalk, all built against the National Standards and all free. I'd like it in the Clearinghouse. Does it clear the bar as you read the criteria? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -669,11 +669,11 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Yanely, you've said the gaps show up long before high school. I wrote the K-5 version: a picture book that teaches spending, because that's the transaction a six-year-old actually performs. Does NGPF ever point teachers to elementary resources, or is that outside the remit? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Yanely — you've said the gaps show up long before high school. I wrote the K-5 version, and it teaches spending because that's the transaction a six-year-old actually performs. Does NGPF ever point teachers below ninth grade, or is that outside the remit? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -719,11 +719,11 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>393</v>
+        <v>348</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Leslie, a question about the Money as You Grow Bookshelf rather than a pitch. The selections skew toward saving and earning. My K-5 book teaches the transaction itself, through the register, sales tax included. Is the shelf still open to new titles, and who evaluates? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Leslie — a Bookshelf question, not a pitch. The Money as You Grow selections skew toward saving and earning. Mine teaches the transaction itself, right through the register. Is the shelf still open, and who does the evaluating? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -769,11 +769,11 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Ken — my picture book and its free K-5 toolkit are aligned to FDIC Money Smart for Young People, and the crosswalk maps every concept to the specific standard. Is there a process for a title to be listed alongside Money Smart materials, or is that not how it works? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ken — my book and its free K-5 toolkit are aligned to Money Smart for Young People, with a crosswalk mapping every concept to the specific standard rather than asking you to take my word. Is there a process for a title to sit alongside Money Smart materials, or is that not how it works? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -819,11 +819,11 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Lyn, is the Money as You Grow Bookshelf still adding titles? I made the K-5 version that teaches spending: comparison shopping, markdowns, coupons, and sales tax at the register. The current shelf is heavy on saving. Happy to send it to whoever evaluates. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Lyn — is the Money as You Grow Bookshelf still taking titles? Mine is K-5 and teaches spending: comparison shopping, markdowns, coupons, sales tax at the register. The current shelf leans heavily toward saving. Happy to send it to whoever evaluates. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -869,11 +869,11 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>375</v>
+        <v>357</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Tracy. A public-private partnership is exactly how a K-5 resource scales, since elementary rarely gets its own budget line. Mine runs 36 pages plus free ungated toolkit, built against five standards frameworks. Is there a fit inside the partnership? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Tracy — a public-private partnership is how a K-5 resource actually scales, since elementary rarely gets its own budget line. It's a 36-page picture book plus free ungated toolkit against five frameworks. Fit inside the partnership? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -919,11 +919,11 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>433</v>
+        <v>395</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Hunter — policy and advocacy at NEFE puts you where the K-5 gap is most visible. Almost everything funded sits at high school. There's a 36-page book behind this with the whole toolkit free for grades 1-5, checked against five frameworks. Is early elementary getting any policy attention, or still nobody's mandate? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Hunter — policy and advocacy at NEFE puts you where the K-5 gap is most visible. Nearly everything funded sits at high school. I wrote a picture book plus free toolkit for grades 1-5 against five frameworks. Is early elementary getting any policy attention, or still an orphan? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -969,11 +969,11 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>395</v>
+        <v>418</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Hi Bill. Tennessee's commission decides what reaches classrooms statewide. I have a K-5 picture book with a free zero-prep toolkit, aligned to Jump$tart, CEE, Common Core, and FDIC Money Smart. Elementary is where the state mandates usually run thin. One line back is plenty. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Bill — Tennessee's commission decides what reaches classrooms statewide, and elementary is usually where state mandates run thin. Mine is a K-5 picture book with a free zero-prep toolkit against Jump$tart, CEE, Common Core, and FDIC Money Smart. Route to get it in front of the commission? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Dave, Wisconsin's Office of Financial Literacy has been at this longer than most states. My K-5 picture book and free toolkit are mapped to five frameworks, crosswalk included. Elementary tends to be the underserved band. Happy to send a copy. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dave — Wisconsin has been at this longer than most states. My K-5 book and free toolkit map to five frameworks. Elementary tends to be the underserved band everywhere I look. Is there a submission route, or a person who reviews outside materials? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>David — as a senior curriculum designer you can tell whether something is built to teach or built to look like it. It's a picture book for grades 1-5 with four zero-prep lessons, assessments, and a 23-row crosswalk, made alongside the book rather than bolted on. Does the design hold? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>David — a senior curriculum designer can tell in five minutes whether something was built to teach or built to look like it was. Mine has four zero-prep lessons, assessments, and a 23-row crosswalk, all written alongside the book rather than bolted on afterward. Does the design hold? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Kevin — a CEE Master Teacher running LifeFinanceEd is the read I want most. My K-5 picture book is aligned to CEE, Jump$tart, Common Core, and FDIC Money Smart, and it leaves saving alone; it teaches spending. Does that framing hold up against how you teach it? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kevin — a CEE Master Teacher running LifeFinanceEd is the read I want most. My K-5 book aligns to CEE, Jump$tart, Common Core, and FDIC Money Smart, and it is a spending book, not a saving one. Does that framing hold up against how you actually teach it? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Beth: a research question. The premise of my K-5 book is that spending competence precedes saving competence developmentally, so we're teaching the wrong skill first. Does that square with what your research and impact work shows, or am I overstating it? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Beth — a research question. My K-5 book argues spending competence precedes saving competence developmentally, which would mean the field teaches the wrong skill first. Does that square with your research and impact work, or am I overstating a tidy story? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1219,11 +1219,11 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>431</v>
+        <v>458</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Hi Laura. Quick one. My K-5 financial literacy toolkit is built against the National Standards, free and completely ungated, and I'd like to list it in the Clearinghouse. Is Suzann Knight the right first stop, or is there a step I'm missing? Endorsed by Wally Luckeydoo, your 2026 Corey Carlisle recipient. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Laura — a Clearinghouse question rather than a pitch. My K-5 toolkit is built against the National Standards, free, ungated, no email capture and no drip campaign. Is Suzann Knight the right first stop, or is there a step I'm skipping? Wally Luckeydoo endorsed the book, which I mention only because he's your 2026 Corey Carlisle recipient. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1269,11 +1269,11 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Gina. A Clearinghouse submission question rather than a pitch. My K-5 toolkit is built against the National Standards and endorsed by Wally Luckeydoo, your 2026 Corey Carlisle Award recipient. Is there anything Jump$tart wants to see beyond the crosswalk before a resource gets listed? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Gina — brand and comms at Jump$tart means you see every resource that wants a logo near it. Mine wants a listing, not a logo. K-5 toolkit against the National Standards, completely free. Anything you need to see beyond the crosswalk before something gets listed? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1319,11 +1319,11 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>389</v>
+        <v>349</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Ryan. A partnerships question rather than a pitch. My K-5 picture book, and the teacher materials cost nothing sits below NGPF's grade band, which might make it complementary rather than competitive. Is elementary something NGPF partners around, or strictly out of scope? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ryan — a partnerships question. My K-5 book plus free toolkit sits below NGPF's grade band, which probably makes it complementary rather than competitive. Is elementary something you partner around, or strictly out of scope? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1369,11 +1369,11 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Billy, a NEFE-shaped question. The research keeps showing money attitudes form by age seven, and almost all the material sits at 9-12. I've written one for grades 1-5 teaching spending rather than saving. Does NEFE ever point people to elementary resources, or is the early band still an open gap? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Billy — a NEFE-shaped question. The research keeps saying money attitudes form by seven, and almost every dollar of material lands at 9-12. I wrote a K-5 picture book teaching spending rather than saving. Does NEFE ever point people to elementary, or is that band still nobody's mandate? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1419,11 +1419,11 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>391</v>
+        <v>364</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Michael, you decide what programming actually reaches people. Mine runs 36 pages, grades 1-5 teaching the whole purchase, right through sales tax, with free zero-prep lessons behind it. Elementary is usually the thinnest shelf. Say the word and it's in the mail. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Michael — you decide what programming actually reaches people. Mine is K-5, teaching the complete purchase, sales tax included, with free zero-prep lessons behind it. Elementary is usually the thinnest shelf in the building. Fit your programming? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1469,11 +1469,11 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Utah — a Utah Jump$tart question. My K-5 picture book and free toolkit are built against the National Standards, with a crosswalk. Elementary is usually where state coalitions have the least to hand teachers. Tell me if it's not a fit. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Hello — a Utah Jump$tart question. My K-5 book and free toolkit are built against the National Standards with a crosswalk. Elementary is usually where state coalitions have the least to hand a teacher. Is there a route to be listed or shared with your network? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -1519,11 +1519,11 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Lorne, you back programs that reach kids at scale. I've written one for grades 1-5 teaching spending rather than saving, with a free zero-prep toolkit behind it. Would it fit anything JumpStart Inc. runs or funds? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Lorne — you back programs that reach kids at scale. Mine is a K-5 picture book teaching spending rather than saving, with a free zero-prep toolkit behind it. Fit anything JumpStart Inc. runs or funds? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1569,11 +1569,11 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>330</v>
+        <v>359</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Hi Ruth. A cheerleader for personal finance education is exactly who I want. My K-5 picture book comes with free ungated content: four lessons, assessments, a 23-row crosswalk. Ignore me if it's wrong for you. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ruth — a self-described cheerleader for personal finance education is exactly who I want reading this. My K-5 book comes with free ungated content: four lessons, assessments, a 23-row crosswalk. Any of it fit your educational content? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -1619,11 +1619,11 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Samantha, as Maine Jump$tart VP you know how thin the elementary shelf is. My K-5 picture book with the whole toolkit free is built against the National Standards. I'll leave it there. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Samantha — as Maine Jump$tart VP you know exactly how thin the elementary shelf is. Mine is K-5 against the National Standards with a free toolkit. Route into what Maine Jump$tart shares with teachers? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -1669,11 +1669,11 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>384</v>
+        <v>324</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Eva — I'm trying to find the right person at the Bureau for a question about the Money as You Grow Bookshelf and whether it still adds titles. There's a K-5 book behind this that skips saving and teaches spending. Send me a one-word reply and I'll act on it. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Eva — I'm trying to find the right person at the Bureau to ask whether the Money as You Grow Bookshelf still adds titles. Mine is a K-5 picture book teaching spending rather than saving. Can you point me? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -1719,11 +1719,11 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Jesse — the Treasurer's outreach reaches families directly, which is where a read-along works best. My K-5 book teaches spending through one purchase, and the free family activity is designed for a kitchen table, not a classroom. I'll post one if it's useful. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jesse — the Treasurer's outreach reaches families directly, which is where a read-along does its best work. Mine teaches spending through one purchase, and the free family activity was built for a kitchen table rather than a classroom. Fit for a Washington program? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -1769,11 +1769,11 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Andrea, you lead digital products for social impact, so you'll know whether a printed picture book is an asset or a liability in 2026. Mine teaches K-5 spending, with free digital lessons behind it. Shout if you want one. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Andrea — you lead digital products for social impact, so you'll know whether a printed picture book is an asset or a liability in 2026. Mine teaches K-5 spending with free digital lessons behind it. Would you tell me straight? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -1819,11 +1819,11 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Sandra: my K-5 picture book and free toolkit are aligned to FDIC Money Smart for Young People, with a full crosswalk. Is there a route for outside materials to be listed or referenced alongside Glad to mail one. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sandra — my K-5 book and free toolkit are aligned to Money Smart for Young People, crosswalk included. Is there a route for outside materials to sit alongside Money Smart, or is that closed by policy? Either answer is useful. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -1873,11 +1873,11 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Christian — teacher success is the whole ballgame, and elementary teachers have almost nothing for financial literacy. I built a free K-5 toolkit around a picture book: four lessons, assessments, a standards crosswalk, no prep. Thirty-six pages; won't cost you an evening. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Christian — teacher success is the whole ballgame, and elementary teachers have close to nothing for financial literacy. I built a free K-5 toolkit around a picture book: four lessons, assessments, a crosswalk, zero prep. Would NGPF ever surface something below ninth grade? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -1927,11 +1927,11 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>367</v>
+        <v>342</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Florida: my K-5 picture book and free ungated toolkit are aligned to the Jump$tart National Standards, with a full crosswalk. Elementary tends to be the thinnest band for coalition resources. Is there a submission route for Florida's network? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Hello — my K-5 book and free ungated toolkit align to the Jump$tart National Standards, crosswalk included. Elementary tends to be the thinnest band for coalition resources. Submission route for Florida's network? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>A premise I'd like tested</t>
+          <t>A premise I'd like punctured</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1981,11 +1981,11 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Hi Dan. As state president you back programs that reach whole communities. Mine runs 36 pages, grades 1-5 with a free toolkit, built against five standards frameworks, teaching kids the complete purchase. If it's a no, no reply needed. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dan — as state president you back programs that reach whole communities. Mine is a K-5 picture book with a free toolkit against five frameworks, teaching kids the complete purchase. Fit with what your organization funds or distributes? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Zero-prep K-5 resource</t>
+          <t>Zero-prep K-5, nothing to reorder</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2035,11 +2035,11 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Aaron. A partnerships question. My K-5 picture book with the whole toolkit free fills the elementary gap most financial-literacy programs leave open, since almost everything is built for high school. I'd rather hear no than nothing. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Aaron — a partnerships question. My K-5 book plus free toolkit fills the elementary gap most financial-literacy programs leave wide open, since almost everything is built for high school. Is early elementary something you partner around? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2089,11 +2089,11 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>385</v>
+        <v>325</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Variny — you decide what's worth putting in front of your partner network. Mine runs 36 pages, grades 1-5 with a free ungated toolkit, built against five standards frameworks. Elementary is the band most partners have nothing for. Copy's yours if you want it. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Variny — you decide what's worth putting in front of a partner network. Mine is K-5 with a free ungated toolkit against five frameworks. Elementary is the band most partners have nothing for. Worth a look? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2143,11 +2143,11 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Meghan, a grants question rather than a pitch. My K-5 picture book has a free toolkit and a grant-ready packet behind it, including cost math for classroom sets. Is early elementary financial literacy something your grants program funds? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Meghan — a grants question rather than a pitch. My K-5 book has a free toolkit and a grant-ready packet with the math already done: 25 copies, $499.75. Is early elementary financial literacy something your grants program funds? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Story idea: what kids' finance skips</t>
+          <t>The half the category skips</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2197,11 +2197,11 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>319</v>
+        <v>349</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Joshua, research and evaluation is where my premise should get tested. I argue spending competence precedes saving competence developmentally, and built a K-5 book around it. I'll send it either way. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Joshua — research and evaluation is exactly where my premise should get tested. I argue spending competence precedes saving competence developmentally. Does that survive scrutiny, or is there literature I've conveniently ignored? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>A gap in kids' money books</t>
+          <t>Cash register or piggy bank?</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2251,11 +2251,11 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Syeda: a CRCM will immediately see the CRA angle: my K-5 book has a grant-ready packet and cost math for classroom sets, which makes it easy for a bank to fund locally. No pitch after this one, promise. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Syeda — a CRCM sees the CRA angle immediately. My K-5 book has a grant-ready packet with cost math already done, which makes it easy for a bank to fund locally and report. Something your board would consider? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -2305,11 +2305,11 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Christopher — as chief program officer you decide what reaches learners. Mine runs 36 pages, grades 1-5 teaching the whole purchase, right through sales tax, with free zero-prep lessons. Elementary is usually the thinnest part of a program. Fit? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Christopher — as chief program officer you decide what reaches learners. Mine is K-5, teaching the complete purchase, sales tax included, with free zero-prep lessons. Elementary is usually the thinnest part of any program. Fit? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -2355,11 +2355,11 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>356</v>
+        <v>319</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>John, as a financial education administrator you decide what gets used. Mine runs 36 pages, grades 1-5 plus free zero-prep toolkit, built against five standards frameworks. Elementary is usually the gap. Would it fit your programs? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>John — as a financial education administrator you decide what actually gets used. Mine is K-5 plus a free zero-prep toolkit against five frameworks. Elementary is usually the gap. Fit your programs? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -2405,11 +2405,11 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>329</v>
+        <v>363</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Jason. A board-level question. Elementary financial literacy is the least funded band and the one the research says matters most. I built a K-5 book and free toolkit for it. One copy, no follow-up, your call. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jason — a board-level question. Elementary financial literacy is the least funded band and the one the research says matters most, which is an odd combination. I built a K-5 book and free toolkit for it. Something your board would want to see? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -2455,11 +2455,11 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>545</v>
+        <v>695</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Alex, a pitch you can reject in one line. The whole category teaches saving. I checked the ABA Foundation's list, all 25 titles: earning, saving, investing. Not one walks a kid through spending. Mine does, including the part where a six-year-old pays sales tax and learns the sticker price was never the price. Planet Money has done the psychology of a purchase for adults. This is the six-year-old version. Happy to send a copy. Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Alex — I read a dozen kids' money books to see where mine fit. Every one taught saving. Save your pennies, save for a rainy day, save, save, save. Not one covered the moment a kid stands there with his own five bucks deciding if the thing is worth it. Am I qualified to fix that? Debatable. I did once talk a cruise-ship shop into a price match and walk out having paid one cent for $300 shoes. Not a typo. Mine runs that whole gauntlet — ad, aisle, markdown, coupon, and the sales tax nobody warns a six-year-old about. Segment, or am I picking a fight the category doesn't want? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -2505,11 +2505,11 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>366</v>
+        <v>283</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Daniel — 360 Parenting reaches families weekly, and spending is where parents and kids collide first, usually in an aisle. My book is that scene, resolved well: the kid compares, chooses the cheaper model, and explains why. I'll send it and get out of your way. The site: https://clarencegetsabargain.com/ · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Daniel — 360 Parenting reaches families weekly, and spending is where parents and kids collide first, usually in an aisle, usually loudly. Mine is that scene, resolved well. Podcast fit? More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -2555,11 +2555,11 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>468</v>
+        <v>527</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Paula: "You can afford anything, but not everything" is the thesis of my book, written for six-year-olds. A kid earns a robot, finds a cheaper older model, and has to decide whether a slightly bigger screen is worth the difference. He picks the cheaper one on purpose. That's the whole climax. Would the I'll post one if it's useful. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Paula — "You can afford anything, but not everything," translated for six-year-olds. Kid earns a robot. Finds the marked-down older model. Slightly smaller screen, no antenna. He takes it anyway and can tell you why. That's the climax — a first grader choosing the cheaper thing on purpose, which is more than most adults manage on Prime Day. Would your crowd want the version they can hand a kid? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -2605,11 +2605,11 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Hi ML. The Noah series shows you know how to carry a lesson without smothering the story. That's my whole anxiety about my own book. Mine teaches money through a boy and a robot. Happy to hear it's not for you. Details at https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>ML — the Noah series shows you can carry a lesson without smothering the story, which is my whole anxiety about my own book. Would you read it as an author and tell me if the lesson shows too much? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -2655,11 +2655,11 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>457</v>
+        <v>436</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>Hi Andrew. 20 million downloads means you've heard every money pitch. Here's mine in one sentence: I wrote the only picture book where the kid pays sales tax. Everything else in this category stops at the piggy bank. Mine runs one purchase end to end, ad to register, for ages 6-10. Is there an episode in "the money book that skips saving entirely"? Everything else: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Andrew — 20 million downloads means you've heard every money pitch ever assembled. Here's mine: I wrote the only picture book where the kid pays sales tax. Everything else stops at the piggy bank. Do I know that for certain? I checked all 25 titles on the ABA Foundation's list, so reasonably certain. Episode, or is the gap imaginary? More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -2705,11 +2705,11 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>359</v>
+        <v>329</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>Randi, Mastermind Parenting is about the hard conversations. Money is one parents dodge because they feel unqualified. My book removes that: the parent just reads the story, and the lesson lands on its own. Would you put it in front of your parents? Details at https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Randi — Mastermind Parenting is about the hard conversations. Money is one parents dodge because they feel unqualified. Mine removes that: the parent reads the story, the lesson lands on its own. Put it in front of your parents? More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -2755,11 +2755,11 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>345</v>
+        <v>306</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>Robert, WE Talk Money for grown-ups; mine is the six-year-old edition. A kid earns a robot, does his own comparison, and talks himself into the cheaper one. Then pays sales tax and learns the sticker lied. Would it work as a segment? Everything else: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Robert — WE Talk Money for grown-ups. Mine is the six-year-old edition. Kid earns a robot, runs his own comparison, talks himself into the cheaper one, then meets sales tax and takes it badly. Segment? More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -2805,11 +2805,11 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>Christopher — Money Matters covers the whole arc of a financial life. I wrote the first chapter of it: a six-year-old's first real purchase, ad to register, sales tax included. I'd rather hear no than nothing. Full story: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Christopher — Money Matters covers a whole financial life. I wrote chapter one: a six-year-old's first real purchase, ad to register, tax at the end. As a bestselling author — does one shopping trip carry 36 pages, or did I stretch it? More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -2855,11 +2855,11 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>David: you built a top-10 personal finance show on thinking clearly about money decisions. Mine is one decision, made by a six-year-old: newer model with a slightly bigger screen, or the marked-down older one. He picks the older one and can say why. Copy's yours if you want it. Everything else: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>David — you built a top-ten show on thinking clearly about money decisions. Mine is one decision, made by a six-year-old: newer model with a slightly bigger screen, or the marked-down older one. He takes the older one and can articulate why. Does that hold up as a teaching case? More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -2905,11 +2905,11 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>355</v>
+        <v>313</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Hi Debbie. You help women in business unlearn money stories they picked up young. I've written one trying to install a better one at six: spend deliberately, compare before you buy, know what the tax adds. Would it land with the families you coach? Full story: https://clarencegetsabargain.com/ · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Debbie — you help women in business unlearn money stories picked up young. Mine tries to install a better one at six: spend on purpose, compare before you buy, know what the register adds. Fit the families you coach? More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -2955,11 +2955,11 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>345</v>
+        <v>304</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>Ellie, Money Talks is the title I wish I'd thought of, because that's the whole design of my book: it's a read-along, so a kid and a grown-up have to have the conversation out loud. It skips saving entirely. I'll send it either way. Everything else: https://clarencegetsabargain.com/ · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ellie — Money Talks is the title I wish I'd taken, because that's the design of mine. It's a read-along, so a kid and a grown-up have to say it out loud. Spending, not saving. Author to author: does it carry? More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -3005,11 +3005,11 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>340</v>
+        <v>308</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>Kerwyn. Author, speaker, podcast host, corporate trainer: you know a money lesson lives or dies on delivery. Mine is delivered as a story about a boy and a robot, and the lesson is spending, which nobody writes about. Would it fit the show? Full story: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kerwyn — author, speaker, podcast host, corporate trainer. You know a money lesson lives or dies on delivery. Mine is delivered as a boy and a robot, and the lesson is spending, which nobody writes about. Show fit? More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -3055,11 +3055,11 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>Joel — you've built a career on the specific mechanics of saving money, coupons, price comparison, the unglamorous stuff. That's literally my plot. A six-year-old reads the ad, finds the markdown, hands over the coupon. No pitch after this one, promise. More at https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Joel — you've built a career on the unglamorous mechanics. Coupons, price comparison, the actual saving of actual money. That's my plot. Six-year-old reads the ad, finds the markdown, hands over the coupon. Interest you or your audience? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>A gap in kids' money books</t>
+          <t>Cash register or piggy bank?</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3109,11 +3109,11 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>407</v>
+        <v>434</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>Amanda — Planet Money is good at the moment a person realizes the economy is doing something to them. I wrote that moment for a six-year-old: he gets to the register and the total is higher than the sticker, because sales tax exists and nobody told him. 36 pages. Is that a segment or just a book? Details at https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Amanda — Planet Money is good at the moment someone realizes the economy just did something to them. Mine is that moment at four feet tall. Kid reaches the register, total's higher than the sticker, and sales tax enters his life uninvited. He takes it personally. 36 pages. Is that a segment or just a strange thing to have made? More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -3159,11 +3159,11 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>369</v>
+        <v>347</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>Chris, you've spent years telling adults what nobody told them at eight. I wrote the book for the eight-year-old. Not saving. Spending: reading the ad first, comparing two models on a shelf, handing over the coupon, paying the tax. Say the word and it's in the mail. More at https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Chris — you've spent years telling adults what nobody told them at eight. I wrote the book for the eight-year-old. Not saving. Spending: read the ad first, compare two models, hand over the coupon, pay the tax. Show fit, or a family you'd hand it to? More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -3209,11 +3209,11 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>357</v>
+        <v>312</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>Tony, financial readiness before life happens is the pitch, and I took it down to age six. The book runs one purchase from sale ad to sales tax. No saving lesson, on purpose, because spending is the skill kids use first. If it's a no, no reply needed. Details at https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Tony — financial readiness before life happens, and I took it down to age six. One purchase, sale ad to sales tax, no saving lesson anywhere in it. Deliberate omission, not an oversight. Podcast fit, or your readers? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -3259,11 +3259,11 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>MaryRuth, author, speaker, podcaster; you'll judge this in a page. I wrote a kids' picture book with a contrarian premise: teach spending, not saving, because spending is what a six-year-old actually does. Ignore me if it's wrong for you. More at https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>MaryRuth — author, speaker, podcaster; you'll judge this in a page. Contrarian premise: teach kids spending, not saving, because spending is what a six-year-old actually does. Does it hold, or am I rationalizing a book I already finished? More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -3309,11 +3309,11 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>332</v>
+        <v>283</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>Frances, coach, author, talk show host. My book is the money conversation for the youngest audience you could have on: a six-year-old who learns that the price on the sticker isn't the price you pay. Would it work as a segment? The site: https://clarencegetsabargain.com/ · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Frances — coach, author, talk show host. Mine is the money conversation for the youngest guest you could book: a six-year-old learning the sticker price was never the price. Segment? More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -3359,11 +3359,11 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>388</v>
+        <v>345</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>Hassan — you take money talks into schools, which is where mine belongs. It's a picture book that teaches spending: comparison shopping, markdowns, coupons, sales tax, all inside a story. Aligned to five frameworks, free zero-prep lessons behind it. One copy, no follow-up, your call. More at https://clarencegetsabargain.com/ · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Hassan — you take money talks into schools, which is where mine belongs. Picture book teaching spending: comparison, markdowns, coupons, sales tax, all inside a story. Five frameworks, free zero-prep lessons, no login. Fit for your school work? More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -3409,11 +3409,11 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>357</v>
+        <v>336</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>Beverly — Your Personal Economy is exactly the frame. Mine is a six-year-old's personal economy: one robot, one budget, one trip, one register. He does the comparison himself and picks the cheaper model. Is there an episode in teaching spending before saving? The site: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Beverly — Your Personal Economy is the exact frame. Mine is a six-year-old's personal economy: one robot, one budget, one aisle, one register. He runs his own comparison and takes the cheaper model. Episode in teaching spending before saving? More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
@@ -3459,11 +3459,11 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Maritere — Mamás411 speaks to parents about raising kids well, and money is the conversation most families put off. My book starts it at six by making it a story, not a lecture. There's a copy with your name on it. Background: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Maritere — Mamás411 speaks to parents about raising kids well, and money is the conversation most families postpone indefinitely. Mine starts it at six by making it a story rather than a lecture. Fit the show? More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -3509,11 +3509,11 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>Whitney. You coach grown-ups out of habits nobody taught them as kids. I wrote the prevention. A six-year-old runs one real purchase start to finish and learns the smarter buy was the older model. Tell me if it's not a fit. Details at https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Whitney — you coach grown-ups out of habits nobody taught them at eight. I wrote the prevention. Six-year-old runs one real purchase, gets it right, walks out feeling competent. That's the entire design. Money Nerds angle, or just a book for your own shelf? More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -3559,11 +3559,11 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>317</v>
+        <v>290</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>Gabriele, "I want it" in a store aisle is a developmental moment as much as a money one. My picture book sits right there and walks a six-year-old from wanting to deciding. Take a look or don't; either is fine. Background: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Gabriele — "I want it" in a store aisle is a developmental moment as much as a money one. Mine sits right there and walks a six-year-old from wanting to deciding. Fit the parents you coach? More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -3609,11 +3609,11 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>328</v>
+        <v>287</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>Leonard, Kids Real Estate and Financial Literacy is after the same kid I am. Mine starts one rung earlier: before a kid can invest, they have to survive a store. The book runs one trip, ad through register. I'll stop there. The site: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Leonard — Kids Real Estate and Financial Literacy is after the same kid. Mine starts one rung earlier: before a kid invests in anything, he has to survive a store. Complement what you teach? More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -3659,11 +3659,11 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>343</v>
+        <v>324</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>Robyn: as a clinical psychologist you'll spot whether a kids' book actually respects the kid. Mine gives a six-year-old a real decision with a real tradeoff and lets him make it. No moral tacked on the end. Would it land with your audience? Background: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Robyn — as a clinical psychologist you'll spot whether a kids' book actually respects the kid. Mine gives a six-year-old a real decision with a real tradeoff and lets him make it. No moral bolted on. Land with your audience? More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -3709,11 +3709,11 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>Hi Jaci. You help parents lead with confidence, and money is where most feel least qualified. My read-along does the teaching so the parent doesn't have to be an expert. Yours if you'll have it. Details at https://clarencegetsabargain.com/ · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jaci — you help parents lead with confidence, and money is where most feel least qualified. My read-along does the teaching so the parent doesn't have to be an expert. Fit the show? More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -3759,11 +3759,11 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>341</v>
+        <v>314</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>Jordan: you get couples onto the same page about money. My book gets a parent and a kid onto the same page, out loud, because it's built as a read-along. Spending, not saving. Would it fit the show or the families you work with? Everything else: https://clarencegetsabargain.com/ · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jordan — you get couples onto the same page about money. Mine gets a parent and a kid onto the same page, out loud, because it's built as a read-along. Spending, not saving. Fit the show or the families you work with? More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -3809,11 +3809,11 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>Hi Tracey. You coach young adults through money nobody taught them. I came at the same problem from the other end, age six, and from the other side of the ledger: spending rather than saving. I'll leave it there. Full story: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Tracey — you coach young adults through money nobody taught them. I came at the same problem from the other end, age six, and the other side of the ledger. Does the framing interest you for Young Money? More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -3859,11 +3859,11 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>304</v>
+        <v>331</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>Sasha, an AFC who hosts a podcast and teaches at Texas Tech is the toughest read I could ask for. The book teaches spending to six-year-olds: compare, catch the markdown, pay the tax. Shout if you want one. More at https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sasha — an AFC who hosts a podcast and teaches at Texas Tech is the toughest read I could ask for. Mine teaches spending to six-year-olds: compare, catch the markdown, pay the tax. Does it hold up, and is there a Financially Inked angle? More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -3909,11 +3909,11 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>298</v>
+        <v>271</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>Lawrence. You take financial literacy on the road. Mine goes into a store: a kid runs one purchase from the sale ad to the register, sales tax and all. Would it fit the audiences you reach? The site: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Lawrence — you take financial literacy on the road. Mine goes into a store: a kid runs one purchase from the sale ad to the register, tax and all. Fit the audiences you reach? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -3959,11 +3959,11 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>305</v>
+        <v>278</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>Michelle, you coach adults toward financial success after the habits are set. Mine tries to set them at six, and it goes at spending instead because that's the skill kids use first. Fit for the podcast? More at https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Michelle — you coach adults toward financial success after the habits have set. Mine tries to set them at six, and it teaches spending because that's what kids do first. Podcast fit? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -4009,11 +4009,11 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>311</v>
+        <v>292</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>Linda. You translate money for real audiences on stage. Mine is the six-year-old translation: one trip, ad through register, sales tax included, told as a story about a boy and a robot. Happy to be told no. The site: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Linda — you translate money for real audiences on stage. Mine is the six-year-old translation: one purchase, ad to register, sales tax included, told as a boy and a robot. Fit your talks? More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -4059,11 +4059,11 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>Sarah — you're a shopping director, so you'll appreciate that my picture book is a shopping story: read the circular, compare two models, use the coupon, pay the tax. It's a kid's first retail education. A copy is easy to send. More at https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sarah — you're a shopping director, so you'll appreciate that my picture book is a shopping story. Read the circular, compare two models, use the coupon, pay the tax. A kid's first retail education. Podcast or coverage fit? More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -4109,11 +4109,11 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>Adam, off your usual beat, but you build media for young people and this is a money book kids finish. It teaches the spending half, through a story about a boy and a robot. Worth a look, or not your lane? The site: https://clarencegetsabargain.com/ · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Adam — off your usual beat, but you build media for young people and this is a money book kids actually finish. Teaches spending rather than saving, through a boy and a robot. Worth a look, or not your lane? More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -4159,11 +4159,11 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>372</v>
+        <v>346</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>Becky — 28 years helping people out of debt means you've traced a lot of it back to habits set young. My book tries to set the good one at six: compare before you buy, know what tax adds, pick the cheaper thing on purpose. Would it fit the families you coach? Everything else: https://clarencegetsabargain.com/ · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Becky — 28 years helping people out of debt means you've traced a lot of it back to habits set at eight. Mine tries to set the good one at six: compare before you buy, know what tax adds, take the cheaper thing on purpose. Fit the families you coach? More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -4209,11 +4209,11 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>338</v>
+        <v>320</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>Russ: completely off your beat, but you know an audience. I wrote a kids' picture book about spending money wisely: a boy, a robot, one trip to the store. Thought it might land with a young reader in your life, or someone who covers this. Full story: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Russ — completely off your beat, but you know an audience. I wrote a kids' picture book about spending money well: a boy, a robot, one trip to the store. Might land with a young reader in your life, or someone who covers this. More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
@@ -4259,11 +4259,11 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>Tami, an award-winning picture book author is the read I want most, because my worry is craft rather than content. The money lesson works; what I need to know is whether the story earns its 36 pages on its own. Would you look at it as a writer, not a subject expert? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Tami — an award-winning picture book author is the read I want most, because my worry is craft, not content. The money lesson works. What I don't know is whether 36 pages about one shopping trip holds a kid on its own merits. Would you read it as a writer rather than a subject expert? Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -4309,11 +4309,11 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>Kim — you've reviewed and edited more children's books than I'll ever write. Mine sneaks a financial education inside a story about a kid and a robot, and I think it works, which is exactly the kind of thing an author is worst at judging. Would you read it as an editor? Happy to trade. Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kim — you've edited and reviewed more children's books than I'll ever write. Mine hides a financial education inside a story about a kid and a robot, and I think it works — which is exactly the judgment an author is least qualified to make about his own book. Would you read it as an editor? Happy to trade. Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -4363,11 +4363,11 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>378</v>
+        <v>485</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>Hi Michelle. You've argued for years the money talk has to start before kids can spell it. I wrote the version for six-year-olds, and it skips saving entirely. It teaches spending: read the ad, compare two models, pay the sales tax. No obligation either way. Press kit: https://clarencegetsabargain.com/press-kit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Michelle — you've said for years the money talk should start before kids can spell it. So I wrote one for six-year-olds with no piggy bank in it. None. It's all spending: read the ad, compare two robots, hand over the coupon, then meet sales tax for the first time. Kids read it for the robot. The rest sneaks in. Column in a kids' money book that skips saving entirely? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -4413,11 +4413,11 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>Stacey: you take books from manuscript to shelf and you'd tell me straight. Mine is a financial literacy picture book that teaches spending instead of saving, ages 6-10, currently selling direct only. I'll stop there. Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Stacey — you take books from manuscript to shelf and you'd tell me straight. Mine teaches spending instead of saving, ages 6-10, selling direct only. Would you look at the positioning and tell me what I'm getting wrong? Press kit: https://clarencegetsabargain.com/press-kit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -4463,11 +4463,11 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>424</v>
+        <v>522</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>Gretchen, far from your beat, and I'll be quick. I read all 25 titles on the ABA Foundation's children's financial literacy list. Every one teaches earning, saving, or investing. None teaches spending. That gap seemed worth filling, so I did. If there's someone at the Times who covers it, I'd take the name. Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Gretchen — nowhere near your beat, so this is short. I read all 25 titles on the ABA Foundation's children's financial literacy list. Every one teaches earning, saving, or investing. None teaches spending, which is the only transaction a six-year-old actually performs. That gap struck me as a matter of first impression, so I wrote the book. If someone at the Times covers this, I'd take the name. Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -4513,11 +4513,11 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>422</v>
+        <v>402</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>Kim. You cover retail; my book is a six-year-old's first walk through one. He reads the circular at the kitchen table, finds the aisle, compares two models on a shelf, hands a coupon to the cashier, and learns about sales tax the hard way. Retail through a first grader's eyes. I'd take a blunt answer. Press kit: https://clarencegetsabargain.com/press-kit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kim — you cover retail. Mine is a six-year-old's first walk through one. Circular at the kitchen table, find the aisle, compare two models, hand a coupon to a cashier, then discover sales tax the hard way. Retail from four feet up, with a robot. Story, or a colleague who'd want it? Press kit: https://clarencegetsabargain.com/press-kit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -4567,11 +4567,11 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>373</v>
+        <v>423</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>Terry — syndicated for decades, so you've seen every kids' money book. Mine breaks the pattern: no saving lesson at all. It teaches spending, because that's the transaction a six-year-old actually performs. 36 pages, ages 6-10. Is there a column in it? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Terry — syndicated for decades means you've seen every kids' money book twice. Mine leaves saving out entirely. Reckless? Possibly. But spending is the transaction a six-year-old performs first, and forty years of piggy banks haven't fixed that. 36 pages, ages 6-10. Column, or am I overselling the gap? Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -4617,11 +4617,11 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>Elizabeth, author, publisher, managing editor: you see the whole path. My kids' picture book leaves saving to everyone else, which puts it in a category of roughly one. Tell me what you make of how to position something with no shelf-mates. Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Elizabeth — author, publisher, managing editor: you see the whole path. Mine leaves saving to everybody else, which puts it in a category of roughly one. I'd take your read on positioning something with no shelf-mates. Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -4667,11 +4667,11 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>359</v>
+        <v>332</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>Sue — you wrote the handbook on self-publishing. Mine is a 36-page full-color picture book teaching kids to spend well, with a free educator toolkit behind it and no Amazon listing by choice. Tell me whether that last decision is brave or dumb. Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sue — you wrote the handbook. Mine is a 36-page full-color picture book with a free educator toolkit and no Amazon listing, by choice. Brave or dumb? I'd genuinely rather have the straight answer than the polite one. Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -4717,11 +4717,11 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>374</v>
+        <v>437</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>Beth: My Mother's Money is about the financial inheritance nobody itemizes. Mine is the earliest deposit into it: a mom teaching a six-year-old to read a sale ad, compare two prices, and understand why the register total is higher. It's a short read. Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Beth — My Mother's Money is about the inheritance nobody itemizes. Mine is the earliest deposit into it: a mother teaching a six-year-old to read a sale ad, compare two prices, and understand why the register total climbed. She also photographs every receipt in the parking lot. Real habit, straight into the book. Column? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -4767,11 +4767,11 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>Julie — you translate markets for a big audience daily. My book translates one purchase for a six-year-old: compare, choose the cheaper model, pay the tax. It's the smallest possible economics story. Say the word and it's in the mail. Press kit: https://clarencegetsabargain.com/press-kit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Julie — you translate markets for a big audience daily. Mine translates one purchase for a six-year-old: compare, take the cheaper model, pay the tax, feel mildly cheated. Smallest possible economics story. Segment, or wrong desk? Press kit: https://clarencegetsabargain.com/press-kit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -4817,11 +4817,11 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>Paul, author to author. There's a 36-page book behind this with a contrarian premise: teach kids spending, not saving, because spending is what they actually do. It reads like a story, not a lesson. I'd like your read on positioning something built to be read for fun. Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Paul — author to author. I wrote a picture book with a contrarian premise: teach kids spending, not saving, because spending is what they actually do. Reads like a story rather than a lesson, or so I tell myself. I'd take your read on positioning something built to be read for fun. Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
@@ -4867,11 +4867,11 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>368</v>
+        <v>352</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>Reyna. You write, speak, and publish in this space. My kids' book takes a contrarian line: spending is the first money skill and no picture book was built around it, so I built one. I want your read on where a spend-first money book finds its audience. Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Reyna — you write, speak, and publish in this space. My kids' book takes a contrarian line: spending is the first money skill and no picture book was built around it, so I built one. Where does a spend-first money book find its audience? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
@@ -4921,11 +4921,11 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>339</v>
+        <v>407</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>Stacy, you cover consumer finance, and I wrote the origin story: a six-year-old's first transaction, complete with the moment he learns sales tax exists. It's a picture book. Send me a one-word reply and I'll act on it. Press kit: https://clarencegetsabargain.com/press-kit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Stacy — you cover consumer finance. I wrote the origin story: a six-year-old's first transaction, including the moment sales tax appears and ruins the arithmetic he'd already done in his head. It's a picture book, which may or may not help my case. Angle here, or a better name at the Times? Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>A premise I'd like tested</t>
+          <t>A premise I'd like punctured</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4975,11 +4975,11 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>349</v>
+        <v>439</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>Veronica, you write about money across a lifetime. This is hour one: a six-year-old runs his first real purchase, ad to register. The parenting hook is that the book teaches the buying adult as much as the kid. Glad to mail one. Press kit: https://clarencegetsabargain.com/press-kit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Veronica — you write about money across a whole life. This is hour one. Six-year-old runs his first purchase, ad to register. The parent hook: his mother photographs every receipt before she pulls out of the parking space. That's in the book because it's a real habit, and it's the one detail adults tell me they recognized. Press kit: https://clarencegetsabargain.com/press-kit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Zero-prep K-5 resource</t>
+          <t>Zero-prep K-5, nothing to reorder</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5029,11 +5029,11 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>388</v>
+        <v>420</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>Ben — you run personal finance coverage, so you decide what's worth a reader's time. Here's the one line: every children's money book teaches saving; mine teaches spending, including sales tax, for ages 6-10. Is there a story in the gap, or someone on the desk who'd take it? Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ben — you run personal finance coverage, so one line: every children's money book teaches saving, mine teaches spending, and the six-year-old pays sales tax on page 22. Did I verify that gap or just assert it? Verified — all 25 titles on the ABA Foundation list. Story, or someone on the desk who'd take it? Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Story idea: what kids' finance skips</t>
+          <t>The half the category skips</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5083,11 +5083,11 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>Annie. You cover the money problems people carry for decades. Most of them start before anyone teaches the basics. My picture book teaches the first one: spending. One purchase, ad to register, for ages 6-10. I'll send it if you're curious. Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Annie — you cover the money problems people carry for thirty years. Most start before anyone teaches anything. Mine teaches the first one: spending. One purchase, ad to register, ages 6-10. Is there a story here, or a better name? Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -5133,11 +5133,11 @@
         </is>
       </c>
       <c r="J92" t="n">
-        <v>376</v>
+        <v>423</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>Stephanie: a segment idea rather than a book pitch. Look at any kids' money book: saving. I checked the ABA Foundation's 25-title list to be sure. Nobody teaches spending, which is what kids actually do. I wrote the one that does. Happy to send a copy. Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Stephanie — segment idea, not a book pitch. Every children's money book teaches saving. I checked the ABA Foundation's 25-title list rather than assume it. Nobody teaches spending, which is what kids actually do with money. I wrote the one that does. Worth a look, or point me at the right producer? Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -5183,11 +5183,11 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>360</v>
+        <v>334</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>Hi Jeff. You cover finance for adults who never got taught this. My book teaches six-year-olds the thing that gets skipped: how to spend a dollar deliberately, through a single purchase, start to checkout. One copy, no follow-up, your call. Press kit: https://clarencegetsabargain.com/press-kit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jeff — you cover finance for adults who were never taught this. Mine teaches six-year-olds the part that gets skipped: how to spend a dollar on purpose, through one purchase, ad to register. Story, or a better contact? Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -5233,11 +5233,11 @@
         </is>
       </c>
       <c r="J94" t="n">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>Renita, award-winning financial journalist who also teaches; you're the ideal test. My contrarian angle: every kids' money book teaches saving, mine teaches spending. Does the framing hold up, or is there a hole in it? Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Renita — an award-winning financial journalist who also teaches is the ideal test. My angle: every kids' money book teaches saving, mine teaches spending. Does the framing hold, or is there a hole in it? Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
@@ -5287,11 +5287,11 @@
         </is>
       </c>
       <c r="J95" t="n">
-        <v>343</v>
+        <v>419</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>Hi Kelli. A senior editor with a CFP will spot a thin premise fast. Mine: spending is the first money skill a kid uses and no picture book is built around it. So I built one. Ages 6-10, sales tax included. Story, or wrong desk? Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kelli — an editor with a CFP spots a thin premise in about four seconds, so here's mine, checkable: spending is the first money skill a kid uses and no picture book is built around it. Does that hold, or have I missed a title? I'd genuinely rather be corrected than published on a false premise. Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
@@ -5341,11 +5341,11 @@
         </is>
       </c>
       <c r="J96" t="n">
-        <v>336</v>
+        <v>317</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>Miranda, Buy Side is about spending well, which is exactly what my book teaches, just to six-year-olds. A kid compares two robots and picks the marked-down one on purpose. Thirty-six pages; won't cost you an evening. Press kit: https://clarencegetsabargain.com/press-kit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Miranda — Buy Side is about spending well. So is my book, just at reading level 620L. A kid compares two robots and takes the marked-down one on purpose. Angle for you, or someone else on the desk? Press kit: https://clarencegetsabargain.com/press-kit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
@@ -5395,11 +5395,11 @@
         </is>
       </c>
       <c r="J97" t="n">
-        <v>378</v>
+        <v>328</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>Lorie — a kids' money book that skips saving entirely and teaches spending instead, including sales tax at the register. Ages 6-10. I think that's a story about what financial education gets wrong, not about my book. Interested, or a better contact at CNBC? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Lorie — a kids' money book that skips saving entirely and teaches spending instead, sales tax and all. The story is what the category ignored for forty years, not my book. Interested, or a better contact at CNBC? Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -5445,11 +5445,11 @@
         </is>
       </c>
       <c r="J98" t="n">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>Gregory, you cover personal finance for people already deep in it. Mine starts at six, and the hook is what it leaves out: no saving lesson at all. Just spending, done properly, once. Happy to hear it's not for you. Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Gregory — you cover personal finance for people already deep in it. Mine starts at six, and the hook is the omission: no saving lesson at all. Just spending, done properly, once. Something here, or a colleague I should ask? Press kit: https://clarencegetsabargain.com/press-kit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>A gap in kids' money books</t>
+          <t>Cash register or piggy bank?</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5499,11 +5499,11 @@
         </is>
       </c>
       <c r="J99" t="n">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>Kamaron — you write for people building money habits right now. My book starts them at six and skips saving and teaches spending. The climax is a kid choosing the cheaper, older model and explaining why. One line back is plenty. Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kamaron — you write for people building money habits right now. Mine starts them at six and skips saving and teaches spending. The climax is a kid taking the cheaper, older model and explaining why. Angle, or a better contact? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
@@ -5553,11 +5553,11 @@
         </is>
       </c>
       <c r="J100" t="n">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>Hi Chris. You've covered family money for years. Here's a small, checkable claim: no children's picture book teaches the complete purchase, through the register, including sales tax. I wrote one that does. Is there a column in what the category skips? Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Chris — you've covered family money for years, so here's a claim you can check over coffee: no children's picture book teaches the complete purchase through the register, sales tax included. Mine does. Is there a column in what the whole category skips? Press kit: https://clarencegetsabargain.com/press-kit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -5607,11 +5607,11 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>Janna, a kids' money book with no saving lesson in it. On purpose. It teaches spending, because that's the transaction a six-year-old performs first. Ages 6-10, 36 pages. I'll post one if it's useful. Press kit: https://clarencegetsabargain.com/press-kit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Janna — a kids' money book with no saving lesson in it. On purpose. It teaches spending, because that's the transaction a six-year-old performs first. 36 pages. Something here, or a better contact? Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
@@ -5661,11 +5661,11 @@
         </is>
       </c>
       <c r="J102" t="n">
-        <v>372</v>
+        <v>339</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>Jennifer. As an editor you'll want the angle, not the book. Mine: children's financial literacy is almost entirely about saving, and it's been that way for forty years, while the skill kids use first is spending. I wrote the counterexample. Interested? Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jennifer — as an editor you'll want the angle. Children's financial literacy is almost entirely about saving, and has been for forty years, while the skill kids use first is spending. I wrote the counterexample. Interested? Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>A premise I'd like tested</t>
+          <t>A premise I'd like punctured</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5715,11 +5715,11 @@
         </is>
       </c>
       <c r="J103" t="n">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>Susie, decades of translating finance for viewers. Mine is the entry-level version: a six-year-old learning that the sticker price isn't what you pay. Tell me if it's not a fit. Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Susie — decades of translating finance for viewers. Mine is the entry-level edition: a six-year-old learning the sticker price was never the price. Segment in teaching money before middle school? Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>A gap in kids' money books</t>
+          <t>Cash register or piggy bank?</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5769,11 +5769,11 @@
         </is>
       </c>
       <c r="J104" t="n">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>Bilal — as an associate editor you'll want the thesis first. Mine: financial literacy education is disproportionately weighted toward saving and investing, while consumer transaction competence is taught almost nowhere. 36 pages, grades 1-5 addressing it. Worth a look? Press kit: https://clarencegetsabargain.com/press-kit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Pandow — the thesis first. Financial literacy education is disproportionately weighted toward saving and investing, while consumer transaction competence is taught almost nowhere. I wrote a K-5 picture book addressing it. Worth a look? Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Zero-prep K-5 resource</t>
+          <t>Zero-prep K-5, nothing to reorder</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5823,11 +5823,11 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>Brooke, you cover consumers and retail on air. My picture book is a kid's first retail transaction: circular, comparison, coupon, sales tax. Ages 6-10. Segment, or a better person on the desk? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Brooke — you cover consumers and retail on air. Mine is a kid's first retail transaction: circular, comparison, coupon, sales tax. Ages 6-10. Segment, or a better person on the desk? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
@@ -5877,11 +5877,11 @@
         </is>
       </c>
       <c r="J106" t="n">
-        <v>309</v>
+        <v>346</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>Jennifer — you cover the machinery of money at the top. I wrote where it starts at the bottom: a six-year-old's first purchase and the moment he discovers sales tax. If it's a no, no reply needed. Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jennifer — you cover the machinery of money at the top. Mine is where it starts at the bottom: a six-year-old's first purchase and the discovery of sales tax. Long shot for your beat, but is there a name you'd point me to? Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
@@ -5931,11 +5931,11 @@
         </is>
       </c>
       <c r="J107" t="n">
-        <v>365</v>
+        <v>333</v>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>Erica: on an editorial board you weigh what's worth covering. Here's a claim I'd stand behind: children's financial literacy has a spending-shaped hole in it. I wrote the book that fills it. Ages 6-10, sales tax at the register. Worth a conversation? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Erica — on an editorial board you weigh what's worth covering. Here's a claim I'd stand behind: children's financial literacy has a spending-shaped hole in it. I wrote the book that fills it. Worth a conversation? Press kit: https://clarencegetsabargain.com/press-kit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -5985,11 +5985,11 @@
         </is>
       </c>
       <c r="J108" t="n">
-        <v>399</v>
+        <v>351</v>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>Hillary. As a curriculum developer and editor you'll see whether the lessons were built alongside the book or bolted on afterward. Mine were built alongside, and I'd like that tested. Four lessons, assessments, a 23-row crosswalk. Send me a one-word reply and I'll act on it. Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Hillary — as a curriculum developer and editor you'll see whether the lessons were written alongside the book or bolted on afterward. Mine were written alongside. Four lessons, assessments, a 23-row crosswalk. Would you test that claim? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -6035,11 +6035,11 @@
         </is>
       </c>
       <c r="J109" t="n">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>Kate, you cover taxes at CNBC, so here's a fact you may enjoy: my children's picture book teaches sales tax. A six-year-old gets to the register, the total is higher than the sticker, and his mom explains where the difference goes. I don't think any other kids' book does it. Story? Press kit: https://clarencegetsabargain.com/press-kit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kate — you cover taxes, so here's a sentence you may enjoy. My children's picture book teaches sales tax. Six-year-old hits the register, the total's higher than the sticker, and his mom explains where the difference goes. I cannot find another kids' book that does it. Story, or just a peculiar thing to have written? Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L109" t="inlineStr"/>
@@ -6085,11 +6085,11 @@
         </is>
       </c>
       <c r="J110" t="n">
-        <v>364</v>
+        <v>329</v>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>Maddie. You cover consumers at Bloomberg. My book is a consumer origin story: a six-year-old's first purchase, from reading the sale ad to paying the tax. It's a picture book, which may or may not be a feature. Story, or is there a better name? Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Maddie — you cover consumers at Bloomberg. Mine is a consumer origin story: a six-year-old's first purchase, sale ad to sales tax. It's a picture book, which may or may not be a feature. Story, or a better contact? Press kit: https://clarencegetsabargain.com/press-kit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
@@ -6135,11 +6135,11 @@
         </is>
       </c>
       <c r="J111" t="n">
-        <v>332</v>
+        <v>297</v>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>Genna — your beat is smart spending and my book is smart spending for six-year-olds. Same subject, different reading level. A kid compares two robots and picks the marked-down one on purpose. I'll send it either way. Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Genna — your beat is smart spending. So is my book, just at reading level 620L. A kid compares two robots and takes the marked-down one on purpose. Story, or a better name on the desk? Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -6185,11 +6185,11 @@
         </is>
       </c>
       <c r="J112" t="n">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>George, a small, checkable claim for a money desk: no children's picture book teaches the complete purchase, sale ad through sales tax. I wrote one. 36 pages, ages 6-10. Fit for the Times, or wrong desk? Press kit: https://clarencegetsabargain.com/press-kit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>George — a checkable claim for a money desk: no children's picture book teaches the complete purchase, sale ad through sales tax. I wrote one. 36 pages, ages 6-10. Fit for the Times, or a better contact? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
@@ -6235,11 +6235,11 @@
         </is>
       </c>
       <c r="J113" t="n">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>Emily, investigations is a long way from a picture book, so I'll be brief. I wrote the only kids' money book I can find that goes at spending instead, including sales tax. If someone on the consumer desk would want it, I'd take the name. Press kit: https://clarencegetsabargain.com/press-kit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Emily — investigations is a long way from a picture book, so briefly. Mine goes at spending instead of saving, sales tax included, and appears to be alone in that. If someone on the consumer desk would want it, I'd take the name. Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L113" t="inlineStr"/>
@@ -6285,11 +6285,11 @@
         </is>
       </c>
       <c r="J114" t="n">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>Ryan — finance and tech is exactly where my book sits: a kid wants the newest robot, then works out that the older marked-down model does the same job. The lesson is that newer isn't better. Ignore me if it's wrong for you. Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ryan — finance and tech is exactly where my book sits. Kid wants the newest robot, then works out the older marked-down model does the same job. The lesson is that newer isn't better, which is heresy in both our fields. Angle for you? Press kit: https://clarencegetsabargain.com/press-kit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L114" t="inlineStr"/>
@@ -6335,11 +6335,11 @@
         </is>
       </c>
       <c r="J115" t="n">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>Christian: quick one. The whole category teaches saving. Mine teaches spending, including the moment a six-year-old learns about sales tax. I think the story is what the category has ignored for forty years. Interested, or a colleague? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Christian — quick one. Every children's money book teaches saving. Mine teaches spending, including the moment a six-year-old meets sales tax. The story is what the category ignored for forty years. Interested, or a colleague? Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L115" t="inlineStr"/>
@@ -6385,11 +6385,11 @@
         </is>
       </c>
       <c r="J116" t="n">
-        <v>351</v>
+        <v>316</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>Wendy, as an editor you've seen every money-book pitch. Mine is contrarian and easy to check: children's financial literacy is all saving, and the skill kids use first is spending. I wrote the one that teaches it. Worth a look? Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Wendy — as an editor you've seen every money-book pitch twice. Mine is contrarian and easy to check: children's financial literacy is all saving, and the skill kids use first is spending. Worth a look? Press kit: https://clarencegetsabargain.com/press-kit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
@@ -6435,11 +6435,11 @@
         </is>
       </c>
       <c r="J117" t="n">
-        <v>337</v>
+        <v>301</v>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>Jessica. An editor with the CFEI will size this up fast. The book teaches spending to ages 6-10: comparison shopping, markdowns, coupons, sales tax, all inside a story. Aligned to five frameworks. I'll leave it there. Press kit: https://clarencegetsabargain.com/press-kit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jessica — an editor with the CFEI sizes this up fast. Mine teaches spending to ages 6-10: comparison, markdowns, coupons, sales tax, all inside a story. Five frameworks. Fit your coverage? Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L117" t="inlineStr"/>
@@ -6485,11 +6485,11 @@
         </is>
       </c>
       <c r="J118" t="n">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>Tobi — you hold the CFEI and write personal finance, so you'll spot fluff. Mine teaches the complete purchase to six-year-olds, sales tax included, which I can't find anywhere else in the category. Shout if you want one. Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Tobi — you hold the CFEI and write personal finance, so you'll spot fluff. Mine teaches the complete purchase to six-year-olds, sales tax included, which I can't find elsewhere in the category. Fit anything you cover? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L118" t="inlineStr"/>
@@ -6535,11 +6535,11 @@
         </is>
       </c>
       <c r="J119" t="n">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>Diane, Savingsmania is about the mechanics of the deal, which is my plot exactly: read the ad, find the markdown, use the coupon. Mine is the six-year-old version. There's a copy with your name on it. Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Diane — Savingsmania is about the mechanics of the deal, which is my plot exactly: read the ad, find the markdown, use the coupon. Mine is the six-year-old edition. Fit your readers? Press kit: https://clarencegetsabargain.com/press-kit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L119" t="inlineStr"/>
@@ -6585,11 +6585,11 @@
         </is>
       </c>
       <c r="J120" t="n">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>Hi Jeffrey. You anchor a show about money and fiduciary care. Mine is the earliest version of the same duty: teaching a six-year-old to check the price before handing over the money. I'll send it and get out of your way. Press kit: https://clarencegetsabargain.com/press-kit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jeffrey — you anchor a show about money and fiduciary care. Mine is the earliest version of the same duty: teaching a six-year-old to check the price before handing over the money. Segment, or not a fit? Press kit: https://clarencegetsabargain.com/press-kit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L120" t="inlineStr"/>
@@ -6635,11 +6635,11 @@
         </is>
       </c>
       <c r="J121" t="n">
-        <v>396</v>
+        <v>435</v>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>Sarah: a children's librarian at NYPL sees more money books than almost anyone. Mine breaks the pattern: no saving lesson, no piggy bank. It teaches spending, and there's a 21-term glossary with page references in the back. Would it circulate? Glad to send a copy. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sarah — a children's librarian at NYPL sees more money books than almost anyone alive. Mine breaks the pattern by having no piggy bank in it. It teaches spending, and there's a 21-term glossary with page references in the back so it doubles as a reference title. Would it circulate? Happy to send a copy. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L121" t="inlineStr"/>
@@ -6685,11 +6685,11 @@
         </is>
       </c>
       <c r="J122" t="n">
-        <v>397</v>
+        <v>427</v>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>Hi Amy. My picture book teaches kids the money skill that never gets a book: spending. Sale ads, comparison, markdowns, sales tax. 36 pages, ages 6-10, Lexile AD 620L, glossary with page refs in the back. Would it earn a spot at Boston Public Library? Happy to send a copy. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Amy — every money book on your shelf ends at the piggy bank. Mine starts at the register: sale ads, comparison, a markdown sticker, a coupon, and the sales tax nobody warns a six-year-old about. AD 620L, 36 pages, 21-term glossary with page refs. Would it circulate at Boston Public, or would it sit? Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L122" t="inlineStr"/>
@@ -6735,11 +6735,11 @@
         </is>
       </c>
       <c r="J123" t="n">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>Devon, KCLS circulation tells you fast what kids actually pick up. Mine is a money book that reads like a story, and it goes at spending instead. Ages 6-10, AD 620L, 21-term glossary. Take a look or don't; either is fine. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Devon — KCLS circulation tells you fast what kids actually pick up versus what adults wish they would. Mine is a money book that reads like a story and teaches the spending half. AD 620L. Would you take a copy and tell me whether it moves? Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L123" t="inlineStr"/>
@@ -6785,11 +6785,11 @@
         </is>
       </c>
       <c r="J124" t="n">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>Elissa. A STEAM innovator and storytime advocate is the right test for a read-aloud. Mine has a genuine comic turn in the middle that kids react to out loud, and it teaches the full transaction, sales tax at the end. Would it work in storytime? Happy to send a copy. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Elissa — a STEAM innovator and storytime advocate is the right test for a read-aloud. Mine has a genuine comic turn in the middle that kids react to out loud, and it teaches the complete purchase, sales tax included. Storytime material, or too transactional? Happy to send a copy. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
@@ -6835,11 +6835,11 @@
         </is>
       </c>
       <c r="J125" t="n">
-        <v>389</v>
+        <v>370</v>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>Mary — as a children's librarian you decide what gets picked up. My book leaves saving alone; it teaches spending, ages 6-10, with a 21-term glossary and page references in the back so it doubles as a reference title. Would it circulate? Glad to send a copy. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Mary — as a children's librarian you decide what gets picked up twice. Mine skips saving and teaches spending, ages 6-10, with a 21-term glossary and page references so it works as a reference title too. Would it circulate? Glad to send a copy. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L125" t="inlineStr"/>
@@ -6885,11 +6885,11 @@
         </is>
       </c>
       <c r="J126" t="n">
-        <v>350</v>
+        <v>397</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>lucianne, a senior children's librarian who mentors others is the read I want. My money book has no piggy bank in it; it teaches the transaction instead, through the register. AD 620L, 36 pages. Yours if you'll have it. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Lucianne — a senior children's librarian who mentors others is the read I want. My money book has no piggy bank in it; it teaches the transaction instead, right through the register. AD 620L, 36 pages. Would you look and tell me where it belongs on your shelves? Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L126" t="inlineStr"/>
@@ -6935,11 +6935,11 @@
         </is>
       </c>
       <c r="J127" t="n">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>Hi Jane. An elementary school librarian sees exactly which books get reshelved and which get hidden under a desk. Mine is a money book built as a read-aloud, with free zero-prep lessons behind it for your teachers. Would it work at Rockford? Glad to send a copy. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jane — an elementary school librarian sees exactly which books get reshelved and which get hidden under a desk. Mine is a money book built as a read-aloud, with free zero-prep lessons behind it for your teachers. Would it work at Rockford? Glad to send a copy. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
@@ -6985,11 +6985,11 @@
         </is>
       </c>
       <c r="J128" t="n">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>Denise, as library director you decide what gets bought. Mine is a hardbound 36-page picture book teaching K-5 financial literacy, AD 620L, with a 21-term glossary. ISBN 979-8-234-07638-0, LCCN 2026906164. Would it fit Duxbury's collection? Happy to send a review copy. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Denise — a library director decides what gets bought, so here are the facts first. Hardbound, 36 pages, full color, AD 620L, 21-term glossary. ISBN 979-8-234-07638-0, LCCN 2026906164. It goes at spending instead of saving. Fit for Duxbury's collection? Happy to send a review copy. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
@@ -7035,11 +7035,11 @@
         </is>
       </c>
       <c r="J129" t="n">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>Olivia — a branch manager knows what actually leaves the building. Mine is a money book kids finish, because it's a story first: a boy, a robot, and one real trip to a store. Ages 6-10. Would it circulate at Northampton? Glad to send a copy. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Olivia — a branch manager knows what actually leaves the building. Mine is a money book kids finish, because it's a story first: a boy, a robot, and one real trip to a store that goes sideways in the middle. Would it circulate at Northampton? Glad to send a copy. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -7085,11 +7085,11 @@
         </is>
       </c>
       <c r="J130" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>Mary: my picture book teaches kids to spend well rather than to save, which puts it in a category of about one. Ages 6-10, AD 620L, 21-term glossary with page references. Would it fit your shelves? Happy to send a copy. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Mary — my picture book teaches kids to spend well rather than to save, which puts it in a category of roughly one. Ages 6-10, AD 620L, 21-term glossary with page references. Fit for your shelves? Happy to send a copy. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L130" t="inlineStr"/>
@@ -7135,11 +7135,11 @@
         </is>
       </c>
       <c r="J131" t="n">
-        <v>449</v>
+        <v>466</v>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>Neale, you built this category. Money Doesn't Grow on Trees was on shelves before most of us were thinking about it. I've written the one that skips saving entirely and teaches spending: a six-year-old runs one purchase, sale ad to register, sales tax included. You'd know in ten pages whether that's a real gap or one I invented. I'll stop there. Background: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Neale — you built this category. Money Doesn't Grow on Trees was on shelves before most of us were thinking about any of it. Mine leaves saving out entirely and teaches spending: one purchase, ad to register, sales tax included. You'd know inside ten pages whether that's a real gap or one I invented to justify a book I wanted to write anyway. Would you tell me straight? More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L131" t="inlineStr"/>
@@ -7185,11 +7185,11 @@
         </is>
       </c>
       <c r="J132" t="n">
-        <v>400</v>
+        <v>444</v>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>Cinders. Moneybunnies covers Earn, Save, Spend, Give across four books. I went deep on one of the four: spending, the whole transaction through the register, in a single story. Author-illustrator to author-illustrator, I'd rather you heard it from me than found it on a shelf. Trade copies? Details at https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Cinders — you got four books out of Earn, Save, Spend, Give. I got greedy and spent all 36 pages on one of them. Spending. The whole transaction, right through the register, sales tax and the small indignity that follows. Author-illustrator to author-illustrator, I'd rather you heard it from me than found it on a shelf and squinted. Trade copies? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L132" t="inlineStr"/>
@@ -7235,11 +7235,11 @@
         </is>
       </c>
       <c r="J133" t="n">
-        <v>345</v>
+        <v>423</v>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>Tiffany, Get Good with Money worked because you refused to talk down to anyone. I tried to hold that line for six-year-olds: a real decision, a real tradeoff, no moral tacked on the end. It teaches the spending half. No obligation either way. More at https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Tiffany — Get Good with Money worked because you refused to talk down to anyone. I tried to hold that line for six-year-olds: real decision, real tradeoff, no moral bolted onto the last page. Mine leaves saving to everybody else. Would you tell me if it condescends? I'd rather hear it from you than from a seven-year-old. More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L133" t="inlineStr"/>
@@ -7285,11 +7285,11 @@
         </is>
       </c>
       <c r="J134" t="n">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>Hi Roda. Smart Money Kids World and Clarence share an audience. Mine is narrow on purpose: one purchase, all the way through the register. As a fellow author and founder, does narrow work better than broad at this age? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Roda — Smart Money Kids World and Clarence share an audience. Mine is narrow on purpose: one purchase, all the way through the register. As a fellow author and founder — does narrow work better at this age? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L134" t="inlineStr"/>
@@ -7335,11 +7335,11 @@
         </is>
       </c>
       <c r="J135" t="n">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>Stephanie: Money Monsters and Clarence are chasing the same 5-10 year old. You came at it teacher-first, I came at it story-first. Mine leaves saving alone; it teaches spending. As a teacher-turned-author, would you tell me if the pedagogy actually holds under the story? Background: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Stephanie — Money Monsters and Clarence are chasing the same five-to-ten-year-old. You came at it teacher-first, I came at it story-first. Mine is a spending book, not a saving one. As a teacher turned author: does the pedagogy survive underneath the story, or does the story eat it? More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L135" t="inlineStr"/>
@@ -7385,11 +7385,11 @@
         </is>
       </c>
       <c r="J136" t="n">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>Hi Sandra. Money Monster Kids and my book share a reader and a mission. Mine goes narrow: one purchase, start to register, sales tax included, rather than a survey of concepts. Send me a one-word reply and I'll act on it. Details at https://clarencegetsabargain.com/ · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sandra — Money Monster Kids and my book share a reader and a mission. Mine goes narrow: one purchase, start to register, rather than a survey of concepts. Fellow author, honest question — does narrow teach more, or less? More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L136" t="inlineStr"/>
@@ -7435,11 +7435,11 @@
         </is>
       </c>
       <c r="J137" t="n">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>Anu, you write children's financial literacy books and simplify economics for kids, so you'll spot a thin premise instantly. Mine: spending is the first money skill and the category ignores it. Glad to mail one. Background: https://clarencegetsabargain.com/ · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Anu — you write children's financial literacy books and simplify economics for kids, so you'll spot a thin premise instantly. Mine: spending is the first money skill and the category ignores it. Does that hold, or is there a book I've missed? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L137" t="inlineStr"/>
@@ -7485,11 +7485,11 @@
         </is>
       </c>
       <c r="J138" t="n">
-        <v>318</v>
+        <v>342</v>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>Lynnette: you've built both a body of work and a network around financial education. 36 pages, grades 1-5 that leaves saving alone; it teaches spending. Tell me where a book like this belongs, and whether FIN is a fit. Full story: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Lynnette — you've built both a body of work and a network around this. Mine is a K-5 picture book teaching spending rather than saving. I'd take your read on where a book like this belongs, and whether FIN is a fit at all. A blunt no is useful too. More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L138" t="inlineStr"/>
@@ -7535,11 +7535,11 @@
         </is>
       </c>
       <c r="J139" t="n">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>Matt — Ask Questions, Save Money, Make More is a skill book. Mine is the same skill, taught at six: ask what it costs, ask if the older one is worse, ask why the total went up. Tell me what you make of positioning a spend-first kids' book with no shelf-mates. Everything else: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Matt — Ask Questions, Save Money, Make More is a skill book. Mine is the same skill at six: ask what it costs, ask whether the older one is actually worse, ask why the total went up at the register. I'd take your read on positioning a spend-first kids' book with no shelf-mates. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L139" t="inlineStr"/>
@@ -7585,11 +7585,11 @@
         </is>
       </c>
       <c r="J140" t="n">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>Maya, you've made a career of making money concepts land for kids. Mine takes the narrow path: one purchase, all the way through the register, rather than a tour of concepts. As a fellow author, does narrow beat broad at this age? Full story: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Maya — you've spent years making money concepts land for kids. I went narrow: one purchase, all the way through the register, instead of a tour of concepts. Does narrow beat broad at this age, or have I just written a thin book with good manners? More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L140" t="inlineStr"/>
@@ -7635,11 +7635,11 @@
         </is>
       </c>
       <c r="J141" t="n">
-        <v>363</v>
+        <v>332</v>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>Jake, Face Your Financial Fears is about the emotional block. Mine tries to prevent one from forming: a six-year-old makes a real money decision, gets it right, and feels competent. That's the whole design. Thirty-six pages; won't cost you an evening. Everything else: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jake — Face Your Financial Fears is about the block that already formed. Mine tries to stop one forming: six-year-old makes a real money decision, gets it right, feels competent. That's the whole design. Author to author, does it work? More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L141" t="inlineStr"/>
@@ -7685,11 +7685,11 @@
         </is>
       </c>
       <c r="J142" t="n">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>Michael, The Money Alphabet and Clarence are after the same kid from different angles: yours builds vocabulary, mine runs one transaction end to end. Author to author, how would you position a spend-first picture book? Happy to trade copies. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Michael — The Money Alphabet and Clarence are after the same kid from different angles: yours builds vocabulary, mine runs one transaction end to end. Author to author, how would you position a spend-first picture book? Happy to trade. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L142" t="inlineStr"/>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>Hi Talaya. Accountant, professor, author: three angles on the same question. Mine is whether a picture book can teach sales tax honestly without boring a six-year-old. I think it can. Happy to be told no. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Talaya — accountant, professor, author: three angles on one question. Mine is whether a picture book can teach sales tax honestly without boring a six-year-old. I think it can. Would you tell me if I'm wrong? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L143" t="inlineStr"/>
@@ -7785,11 +7785,11 @@
         </is>
       </c>
       <c r="J144" t="n">
-        <v>368</v>
+        <v>412</v>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>Ronald, you built a financial literacy curriculum, so you know what teachers actually pick up. Mine runs 36 pages with four zero-prep lessons behind it, aimed at K-5 where most curricula don't reach. Would it complement Responsible Money? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ronald — you built a financial literacy curriculum, so you know what teachers actually pick up versus what they politely accept. It's a 36-page picture book with four zero-prep lessons, aimed at K-5 where most curricula don't reach. Complement Responsible Money, or compete with it? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L144" t="inlineStr"/>
@@ -7835,11 +7835,11 @@
         </is>
       </c>
       <c r="J145" t="n">
-        <v>334</v>
+        <v>376</v>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>Fernando, principal, author, and coach: you see the whole building. My K-5 book teaches spending through a story, with free standards-aligned lessons. Would it work at Robert F. Let me know and it ships. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Branch — principal, author, and coach means you see the whole building at once. Mine teaches spending through a story, with free standards-aligned lessons behind it. Would it work at Robert F. Smith STEAM Academy, and where would you slot it? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L145" t="inlineStr"/>
@@ -7885,11 +7885,11 @@
         </is>
       </c>
       <c r="J146" t="n">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>Anthony. A CFP who writes children's books is a rare combination and exactly the read I want. Mine teaches the complete purchase to six-year-olds, sales tax included. Does it get the money right, and does the story survive the accuracy? Happy to trade copies. Details at https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Anthony — a CFP who writes children's books is a rare combination and exactly the read I need. Mine teaches the complete purchase to six-year-olds, sales tax included. Does it get the money right, and does the story survive the accuracy? Happy to trade copies. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L146" t="inlineStr"/>
@@ -7935,11 +7935,11 @@
         </is>
       </c>
       <c r="J147" t="n">
-        <v>272</v>
+        <v>307</v>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>Tiffany. A CFEI who writes for kids and coaches youth is a triple read. Mine teaches the complete purchase to ages 6-10, sales tax included. One line back is plenty. Everything else: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Tiffany — a CFEI who writes for kids and coaches youth is a triple read. Mine teaches the complete purchase to ages 6-10, sales tax included. Does it hold as instruction, or is the story doing all the work? More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L147" t="inlineStr"/>
@@ -7985,11 +7985,11 @@
         </is>
       </c>
       <c r="J148" t="n">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>Pamela. The Money Lady and a fellow author; you make money approachable for a living. Mine does it for six-year-olds by teaching spending rather than saving. If it's a no, no reply needed. Full story: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Pamela — The Money Lady and a fellow author; you make money approachable for a living. Mine does it for six-year-olds by teaching spending rather than saving. Does the story carry the lesson, or is it doing too much? More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L148" t="inlineStr"/>
@@ -8035,11 +8035,11 @@
         </is>
       </c>
       <c r="J149" t="n">
-        <v>344</v>
+        <v>313</v>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>Cashem — you're building youth financial literacy from the ground up, so we're after the same kid. Mine runs 36 pages plus free zero-prep toolkit for K-5, which is the band almost nobody serves. Does it fit anything you're building? Everything else: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Cash — you're building youth financial literacy from the ground up, so we're after the same kid. I made a picture book plus free zero-prep toolkit for K-5, the band almost nobody serves. Fit anything you're building? More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L149" t="inlineStr"/>
@@ -8085,11 +8085,11 @@
         </is>
       </c>
       <c r="J150" t="n">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>Tonia, an author and financial wellness partner meets families where money gets real. Mine teaches a six-year-old the complete purchase, and the free family activity is built for a kitchen table. I'd rather hear no than nothing. Full story: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Tonia — an author and financial wellness partner meets families where money gets real. Mine teaches a six-year-old the complete purchase, and the free family activity was built for a kitchen table. Fit the families you work with? More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L150" t="inlineStr"/>
@@ -8135,11 +8135,11 @@
         </is>
       </c>
       <c r="J151" t="n">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>Prerna, Mom, Money &amp; Mindset and Clarence are after the same household. Mine is a read-along, so the parent and kid do it together and the money conversation follows naturally. Copy's yours if you want it. Everything else: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Prerna — Mom, Money &amp; Mindset and Clarence are after the same household. Mine is a read-along, so the parent and kid do it together and the money conversation follows without anyone announcing it. Fit what your foundation reaches? More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L151" t="inlineStr"/>
@@ -8185,11 +8185,11 @@
         </is>
       </c>
       <c r="J152" t="n">
-        <v>321</v>
+        <v>288</v>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>Kathy — as a parent educator you know money is the topic parents dodge because they feel unqualified. My read-along removes that: the parent just reads the story. Would you put it in front of the parents you coach? Full story: https://clarencegetsabargain.com/ · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kathy — as a parent educator you know money is the topic parents dodge because they feel unqualified to teach it. My read-along removes that entirely. Put it in front of the parents you coach? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L152" t="inlineStr"/>
@@ -8235,11 +8235,11 @@
         </is>
       </c>
       <c r="J153" t="n">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>Jessie — as an author-illustrator running your own imprint, you'll judge both halves. Mine is written and illustrated by me, which is either an advantage or a problem, and I can't tell which. Happy to send a copy. Background: https://clarencegetsabargain.com/ · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jessie — as an author-illustrator running your own imprint you'll judge both halves. Mine is written and illustrated by me, which is either an advantage or a problem, and I genuinely can't tell which. Would you say? More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L153" t="inlineStr"/>
@@ -8285,11 +8285,11 @@
         </is>
       </c>
       <c r="J154" t="n">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>Miranda, children's author to children's author. Mine hides a financial education inside a story about a boy and a robot, and my fear is that the education shows. Would you read it and tell me where it pokes through? Details at https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Miranda — children's author to children's author. Mine hides a financial education inside a story about a boy and a robot, and my fear is that the education shows. Would you read it and tell me where it pokes through? More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L154" t="inlineStr"/>
@@ -8335,11 +8335,11 @@
         </is>
       </c>
       <c r="J155" t="n">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>Suzy, an award-winning children's author will spot craft problems a subject expert misses. Mine teaches money, but what I need judged is the story: does a 36-page arc about one shopping trip actually hold a six-year-old? Happy to send a copy. Everything else: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Suzy — an award-winning children's author spots craft problems a subject expert misses entirely. Mine teaches money, but what I need judged is the story: does a 36-page arc about one shopping trip hold a six-year-old? Happy to send a copy. More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L155" t="inlineStr"/>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>A premise I'd like tested</t>
+          <t>A premise I'd like punctured</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -8389,11 +8389,11 @@
         </is>
       </c>
       <c r="J156" t="n">
-        <v>379</v>
+        <v>326</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>f. You wrote Budgeting For Dummies and Personal Finance For Teens, so you've covered the ages on either side of mine. Six to ten is the gap between them. My book teaches spending there. Does that age band actually need its own book, or am Happy to hear it's not for you. The site: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Athena — you wrote Budgeting For Dummies and Personal Finance For Teens, so you've covered the ages on either side of mine. Six to ten is the gap between them. Does that band need its own book, or am I inventing a market? More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L156" t="inlineStr"/>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>Bertram: From Piggy Banks to Portfolios runs K-12 programs, so we're literally in the same aisle. Mine is the bottom rung: before the piggy bank, a kid has to survive a store. I'll send it either way. Background: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Bertram — From Piggy Banks to Portfolios runs K-12 programs, so we're literally in the same aisle. Mine is the bottom rung: before the piggy bank, a kid has to survive a store. Fit your school programs? More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L157" t="inlineStr"/>
@@ -8489,11 +8489,11 @@
         </is>
       </c>
       <c r="J158" t="n">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>Hi Andi. Author, coach, money mentor. Mine is the children's version of the same work: install one good habit at six rather than repair it at thirty-six. Would you point families toward it? Details at https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Andi — author, coach, money mentor. Mine is the children's version of the same work: install one good habit at six rather than repair it at thirty-six. Point families toward it? More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L158" t="inlineStr"/>
@@ -8539,11 +8539,11 @@
         </is>
       </c>
       <c r="J159" t="n">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>Anna, Money Mentor and a CFEI; you'll judge fast. Mine teaches K-5 spending rather than saving, checked against five frameworks. No pitch after this one, promise. Background: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Anna — Money Mentor and a CFEI; you'll judge fast. Mine teaches K-5 spending rather than saving, against five frameworks. Fit the people Mentora reaches? More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L159" t="inlineStr"/>
@@ -8589,11 +8589,11 @@
         </is>
       </c>
       <c r="J160" t="n">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>Gordon. Cashflow Cookbook is about the unglamorous mechanics that actually add up. My book teaches the same mechanics to six-year-olds: compare, use the coupon, notice the tax. Ignore me if it's wrong for you. Details at https://clarencegetsabargain.com/ · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Gordon — Cashflow Cookbook is about the unglamorous mechanics that actually add up. Mine teaches the same mechanics to six-year-olds: compare, use the coupon, notice the tax. Fit your talks, or a family you'd recommend it to? More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L160" t="inlineStr"/>
@@ -8639,11 +8639,11 @@
         </is>
       </c>
       <c r="J161" t="n">
-        <v>316</v>
+        <v>289</v>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>Mapalo — a bestselling personal finance author knows what makes money land. Mine goes for the youngest possible audience and leaves saving alone; it teaches spending. Author to author, does the premise carry? Background: https://clarencegetsabargain.com/ · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Mapalo — a bestselling personal finance author knows what makes money land. Mine goes for the youngest possible audience and teaches the spending half. Author to author: does the premise carry? More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L161" t="inlineStr"/>
@@ -8689,11 +8689,11 @@
         </is>
       </c>
       <c r="J162" t="n">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>Kathryn, Money Savvy and Clarence are after the same kid. Mine is narrow: one purchase, sale ad to sales tax. As an award-winning author in this space, does going narrow teach more than going broad? Details at https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kathryn — Money Savvy and Clarence are after the same kid. Mine is narrow: one purchase, sale ad to sales tax. As an award-winning author in this space — does narrow teach more than broad? More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L162" t="inlineStr"/>
@@ -8739,11 +8739,11 @@
         </is>
       </c>
       <c r="J163" t="n">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>Jeahne, educator, author, speaker; you know how to make money click. Mine does it for six-year-olds through one shopping trip rather than a set of lessons. Fellow author: does the story carry the teaching? Everything else: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jeahne — educator, author, speaker; you know how to make money click. Mine does it for six-year-olds through one shopping trip rather than a set of lessons. Fellow author: does the story carry the teaching? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L163" t="inlineStr"/>
@@ -8789,11 +8789,11 @@
         </is>
       </c>
       <c r="J164" t="n">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>Andrew — a bestselling author building financial wellness programs will size this up fast. Mine is the earliest intervention possible: age six, spending rather than saving. I'll leave it there. Full story: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Andrew — a bestselling author building financial wellness programs sizes this up fast. Mine is the earliest intervention available: age six, spending rather than saving. How would you position it? More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L164" t="inlineStr"/>
@@ -8839,11 +8839,11 @@
         </is>
       </c>
       <c r="J165" t="n">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>Jane: as a financial therapist you know money is emotional long before it's mathematical. My book meets a kid at the first feeling, wanting something in a store, and walks him to a decision he makes himself. Shout if you want one. Everything else: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jane — as a financial therapist you know money is emotional long before it's mathematical. Mine meets a kid at the first feeling, wanting something in a store, and walks him to a decision he makes himself. Does that land clinically? More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L165" t="inlineStr"/>
@@ -8889,11 +8889,11 @@
         </is>
       </c>
       <c r="J166" t="n">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>Hi Allen. You meet people after the habits have set. Mine tries to set a good one at six: compare before you buy, and know what the register adds. Would it fit the families you serve? Full story: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Allen — you meet people after the habits have set. Mine tries to set a good one at six: compare before you buy, and know what the register adds. Fit the families you serve? More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L166" t="inlineStr"/>
@@ -8939,11 +8939,11 @@
         </is>
       </c>
       <c r="J167" t="n">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>Elisabeth, you guide adults through money; mine starts two decades earlier. It teaches a six-year-old to compare two prices and choose deliberately. There's a copy with your name on it. Everything else: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Elisabeth — you guide adults through money; mine starts two decades earlier. It teaches a six-year-old to compare two prices and choose deliberately. Would the families you work with hand it to their kids? More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L167" t="inlineStr"/>
@@ -8989,11 +8989,11 @@
         </is>
       </c>
       <c r="J168" t="n">
-        <v>309</v>
+        <v>270</v>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>John. You build learning that scales globally. Mine runs 36 pages, grades 1-5 with a free zero-prep toolkit behind it, built against five standards frameworks. Does the approach fit what Electus builds? Full story: https://clarencegetsabargain.com/ · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>John — you build learning that scales globally. Mine is K-5 with a free zero-prep toolkit against five frameworks. Does the approach fit what Electus builds, or duplicate it? More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L168" t="inlineStr"/>
@@ -9039,11 +9039,11 @@
         </is>
       </c>
       <c r="J169" t="n">
-        <v>413</v>
+        <v>516</v>
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>Annamaria — your work established how early the gaps form and how durable they are. 36 pages, grades 1-5 on the premise that spending competence precedes saving competence developmentally, so the field may be teaching the wrong skill first. Take a look or don't; either is fine. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Professor Lusardi — your work established how early these gaps open and how stubbornly they stay open. I've written a K-5 picture book on a premise I'd like you to puncture if it deserves it: we teach children saving first, but spending is the transaction they actually perform, so the sequence may be backwards. I'm an attorney who draws robots, not a researcher. Tell me if I'm overreaching. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L169" t="inlineStr"/>
@@ -9089,11 +9089,11 @@
         </is>
       </c>
       <c r="J170" t="n">
-        <v>391</v>
+        <v>360</v>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>Kate, a professor of practice with an AFC will test the premise properly. Mine: we teach kids saving first, but spending is the transaction they actually perform, so the sequencing is backwards. I wrote the K-5 counterexample. I'll send it and get out of your way. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kate — a professor of practice with an AFC tests a premise properly. Mine: we teach kids saving first, but spending is the transaction they actually perform, so the sequencing is backwards. I wrote the K-5 counterexample. Does it hold? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L170" t="inlineStr"/>
@@ -9139,11 +9139,11 @@
         </is>
       </c>
       <c r="J171" t="n">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>Susan, you've directed a center for economic education for years. My K-5 picture book argues the elementary band is underserved because everything gets built for high school. It's aligned to CEE and four other frameworks. Does that match what you see? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Susan — you've directed a center for economic education for years. My K-5 book argues the elementary band is underserved because everything gets built for high school. Aligned to CEE and four others. Does that match what you see? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L171" t="inlineStr"/>
@@ -9189,11 +9189,11 @@
         </is>
       </c>
       <c r="J172" t="n">
-        <v>378</v>
+        <v>345</v>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>Scott — as a researcher you'll want the claim tested. Mine: consumer transaction competence is taught almost nowhere in K-5, despite being the money behavior kids perform first. I built a book and toolkit around it. Yours if you'll have it. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Scott — as a researcher you'll want the claim tested. Mine: consumer transaction competence is taught almost nowhere in K-5, despite being the money behavior kids perform first. Is there literature contradicting me? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L172" t="inlineStr"/>
@@ -9243,11 +9243,11 @@
         </is>
       </c>
       <c r="J173" t="n">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
-          <t>Alison, early elementary curriculum plus research is the exact combination that would catch a flaw in my premise. I argue spending is developmentally the first money skill and the field teaches saving instead. Does that hold at the early-elementary level? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Alison — early elementary curriculum plus research is the combination most likely to catch a flaw in my premise. I argue spending is developmentally the first money skill and the field teaches saving instead. Does that hold at early-elementary level? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L173" t="inlineStr"/>
@@ -9293,11 +9293,11 @@
         </is>
       </c>
       <c r="J174" t="n">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>Charlotte: you research children and digital money, which is the next chapter of my book, literally. Mine teaches the physical transaction: cash, coupon, register, sales tax. Does teaching the tangible version still matter when kids see tap-to-pay first? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Charlotte — you research children and digital money, which is literally the next chapter of my book. Mine teaches the physical transaction: cash, coupon, register, tax. Does teaching the tangible version still matter when kids see tap-to-pay first? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L174" t="inlineStr"/>
@@ -9344,11 +9344,11 @@
         </is>
       </c>
       <c r="J175" t="n">
-        <v>328</v>
+        <v>395</v>
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
-          <t>Alexander, you're training for elementary education, which makes you closer to this than most people I'm asking. My K-5 book teaches money through a story about a boy and a robot. It's a short read. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Alexander — you're training for elementary education, which makes you closer to this than most people I'm asking. Mine teaches money through a story about a boy and a robot. Does it read like something a real first grader would sit through, or does the lesson show? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L175" t="inlineStr"/>
@@ -9394,11 +9394,11 @@
         </is>
       </c>
       <c r="J176" t="n">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>Purnendu — you work in youth financial literacy and you're close to the age group. My book teaches six-year-olds to spend well rather than to save. Does it read like something a real kid would finish, or does the lesson show? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Purnendu — you work in youth financial literacy and you're close to the age group. Mine teaches six-year-olds to spend well rather than to save. Does it read like something a real kid finishes, or does the teaching poke through? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L176" t="inlineStr"/>
@@ -9448,11 +9448,11 @@
         </is>
       </c>
       <c r="J177" t="n">
-        <v>383</v>
+        <v>349</v>
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
-          <t>Amy, a credit-union-backed financial success center sees where the gaps started. Mine tries to close one at six, and there's a grant-ready packet with cost math for classroom sets if VCU or the credit union wanted to fund a local set. Worth a look? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Amy — a credit-union-backed financial success center sees where the gaps started. Mine tries to close one at six, and there's a grant packet with cost math if VCU or the credit union wanted to fund a local set. Worth a look? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L177" t="inlineStr"/>
@@ -9498,11 +9498,11 @@
         </is>
       </c>
       <c r="J178" t="n">
-        <v>433</v>
+        <v>395</v>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>Bethann: a bankers association reaches classrooms and families at once, which is the distribution a K-5 book needs. Mine is checked against five frameworks with free zero-prep lessons, and there's a grant-ready packet if a member bank wanted to fund classroom sets. Thirty-six pages; won't cost you an evening. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Bethann — a bankers association reaches classrooms and families at once, which is the distribution a K-5 book needs and rarely gets. Mine is five frameworks, free zero-prep lessons, plus a grant packet if a member bank wanted to fund classroom sets. Fit Utah's outreach? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L178" t="inlineStr"/>
@@ -9548,11 +9548,11 @@
         </is>
       </c>
       <c r="J179" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
-          <t>Ruben, my picture book and toolkit are aligned to the CEE standards with a full crosswalk. Is there a route for a K-5 title to be listed in CEE's resource library or I'll send it if you're curious. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ruben — my book and toolkit are aligned to the CEE standards with a full crosswalk. Is there a route for a K-5 title into CEE's resource library or EconEdLink, and what would you want to see first? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L179" t="inlineStr"/>
@@ -9598,11 +9598,11 @@
         </is>
       </c>
       <c r="J180" t="n">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>Saskia. Promise Academy is deliberate about what earns classroom time. My K-5 book teaches one purchase end to end, tax and all, and the family activity is built for a kitchen table. Would it fit your classrooms or your family programming? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Saskia — Promise Academy is deliberate about what earns classroom time, which is the right instinct. Mine teaches the complete purchase, sales tax included, and the family activity was built for a kitchen table. Classrooms or family programming — or neither? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L180" t="inlineStr"/>
@@ -9648,11 +9648,11 @@
         </is>
       </c>
       <c r="J181" t="n">
-        <v>364</v>
+        <v>380</v>
       </c>
       <c r="K181" s="2" t="inlineStr">
         <is>
-          <t>Hi Jillian. Intuit for Education is built around real financial decisions, which is my book's whole structure: a single purchase, start to checkout, sales tax included. Mine sits at K-5, below your usual band. I'd take a blunt answer. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jillian — Intuit for Education is built around real financial decisions, which is my book's entire structure: one purchase, ad to register, sales tax included. Mine sits at K-5, below your usual band. Does the framing match how you think about curriculum? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L181" t="inlineStr"/>
@@ -9698,11 +9698,11 @@
         </is>
       </c>
       <c r="J182" t="n">
-        <v>426</v>
+        <v>401</v>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>Thomas, Montgomery County sets what reaches a lot of classrooms. I've written one for grades 1-5 with a free zero-prep toolkit, mapped to five frameworks, crosswalk included, no consumables to reorder. The honest question is placement: classroom, library, or family night. A copy is easy to send. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Taylor — Montgomery County sets what reaches a lot of classrooms. Mine is a K-5 picture book with a free zero-prep toolkit, five frameworks, nothing consumable to reorder next August. The honest question is placement rather than merit: classroom, library, or family night? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L182" t="inlineStr"/>
@@ -9748,11 +9748,11 @@
         </is>
       </c>
       <c r="J183" t="n">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="K183" s="2" t="inlineStr">
         <is>
-          <t>Sandhya, Literary Safari builds inclusive media that respects kids, which is the bar I was aiming for. My book gives a six-year-old a real financial decision with a real tradeoff and lets him make it himself. I want your read on positioning. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sandhya — Literary Safari builds media that respects kids, which was the bar I aimed at. Mine gives a six-year-old a real financial decision with a real tradeoff and lets him make it himself. I'd take your read on positioning. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L183" t="inlineStr"/>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>Penelope — a superintendent who's a lifelong learner is the read I want. Mine runs 36 pages, grades 1-5 plus free standards-aligned lessons, and elementary is where financial literacy usually gets skipped entirely. I'll stop there. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Martin-Knox — a superintendent who's a lifelong learner is the read I hoped for. Mine is K-5 with free standards-aligned lessons, and elementary is where financial literacy gets politely skipped. Where would it fit in your district? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L184" t="inlineStr"/>
@@ -9848,11 +9848,11 @@
         </is>
       </c>
       <c r="J185" t="n">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
-          <t>Cortez, you've stabilized whole systems, so you know which resources survive contact with a real building. I made a picture book with zero-prep lessons and nothing to reorder. Would it hold up in a K-12 setting, or is it too small to matter? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. McCoy — you've stabilized whole systems, so you know which resources survive contact with an actual building. I wrote a picture book with zero-prep lessons and nothing to reorder. Does it hold up at K-12 scale, or is it too small to matter? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L185" t="inlineStr"/>
@@ -9898,11 +9898,11 @@
         </is>
       </c>
       <c r="J186" t="n">
-        <v>356</v>
+        <v>404</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>Denise — as director of elementary curriculum you decide what reaches K-5, which is exactly the band financial literacy skips. Mine runs 36 pages with a 23-row standards crosswalk and four zero-prep lessons. No obligation either way. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Denise — financial literacy politely skips K-5 and turns up in ninth grade acting surprised. Mine doesn't. 36 pages, four zero-prep lessons, a 23-row crosswalk you can check rather than take on faith, and a K-5 teacher with 30+ years who told me what to cut. Clear your bar? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L186" t="inlineStr"/>
@@ -9948,11 +9948,11 @@
         </is>
       </c>
       <c r="J187" t="n">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
-          <t>Sarai: a Spanish immersion magnet raises a question I should ask directly: my book is English-only right now, though the free companion activities have a Spanish toggle. Would it still work in your classrooms, or does that limit it too much? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sarai — a Spanish immersion magnet raises a question I should ask outright: the book is English-only, though the free companion activities have a Spanish toggle. Does that limit it too much for your classrooms, or does it still work? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L187" t="inlineStr"/>
@@ -9998,11 +9998,11 @@
         </is>
       </c>
       <c r="J188" t="n">
-        <v>344</v>
+        <v>376</v>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>Dr — 4MQ builds financial literacy frameworks for early childhood, which is the band almost nobody serves. It's a picture book for grades 1-5 plus free toolkit checked against five frameworks. Glad to mail one. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Richard — 4MQ builds financial literacy frameworks for early childhood, which is the band almost nobody serves. Mine is a K-5 picture book plus free toolkit against five frameworks. Does the approach fit what you're building, or duplicate it? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L188" t="inlineStr"/>
@@ -10048,11 +10048,11 @@
         </is>
       </c>
       <c r="J189" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
-          <t>Hi Natasha. PiggyyBank and Clarence are after the same kid. Mine is the analog version: a printed read-along that teaches the whole transaction, sales tax included. I'll send it if you're curious. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Natasha — PiggyyBank and Clarence are after the same kid. Mine is the analog version: a printed read-along teaching the whole transaction, sales tax included. Complementary, or are we in each other's way? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L189" t="inlineStr"/>
@@ -10098,11 +10098,11 @@
         </is>
       </c>
       <c r="J190" t="n">
-        <v>366</v>
+        <v>323</v>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>Vince, NFEC reaches thousands of instructors, and the K-5 band is where most of them have the least material. My picture book with the whole toolkit free is checked against five frameworks with a full crosswalk. Is there a route into the NFEC resource network? Details at https://clarencegetsabargain.com/ · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Vince — NFEC reaches thousands of instructors, and K-5 is where most of them have the least to hand anyone. Mine runs 36 pages plus free toolkit against five frameworks, crosswalk included. Route into the NFEC resource network? More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L190" t="inlineStr"/>
@@ -10148,11 +10148,11 @@
         </is>
       </c>
       <c r="J191" t="n">
-        <v>405</v>
+        <v>380</v>
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
-          <t>Sam — twenty-plus years and a quarter million kids means you've seen every approach. Sammy teaches saving beautifully. I went the other direction and taught spending, on the theory it's what a six-year-old does first. Fellow builder to fellow builder: is that a real gap or a rationalization? Everything else: https://clarencegetsabargain.com/ · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sam — twenty-plus years and a quarter million kids means you've seen every approach in this space. Sammy teaches saving beautifully. I went the other way on the theory that spending is what a six-year-old does first. Real gap, or a convenient story I tell myself? You'd know. More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L191" t="inlineStr"/>
@@ -10198,11 +10198,11 @@
         </is>
       </c>
       <c r="J192" t="n">
-        <v>346</v>
+        <v>313</v>
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>Karen — GiftingSense teaches kids to think before buying, which is my book's entire plot. A six-year-old compares two robots and talks himself into the cheaper one. We're solving the same problem in different formats. Worth comparing notes? Details at https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Karen — GiftingSense teaches kids to think before buying, which is my book's entire plot. A six-year-old compares two robots and talks himself into the cheaper one. Same problem, different format. Worth comparing notes? More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L192" t="inlineStr"/>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>Story idea: what kids' finance skips</t>
+          <t>The half the category skips</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -10252,11 +10252,11 @@
         </is>
       </c>
       <c r="J193" t="n">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
-          <t>Hi Elizabeth. You write personal finance for people well past first grade. Mine starts there, and the angle is the omission: no children's money book teaches spending. Mine does, sales tax and all. I'd rather hear no than nothing. Details at https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Elizabeth — you write personal finance for people well past first grade. Mine starts there, and the angle is the omission: no children's money book teaches spending. Mine does, sales tax and all. Story, or a better contact? More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L193" t="inlineStr"/>
@@ -10306,11 +10306,11 @@
         </is>
       </c>
       <c r="J194" t="n">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>Kate, as a lead writer and spokesperson you get asked for kids' money resources constantly. Here's one that's different: it skips saving entirely, and takes a six-year-old through the register. Free classroom materials behind it. Copy's yours if you want it. Everything else: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kate — as a lead writer and spokesperson you get asked for kids' money resources constantly. Here's one that's different: it teaches spending, not saving, and takes a six-year-old through the register. Free classroom materials behind it. Worth knowing about? More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L194" t="inlineStr"/>
@@ -10356,11 +10356,11 @@
         </is>
       </c>
       <c r="J195" t="n">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="K195" s="2" t="inlineStr">
         <is>
-          <t>Prince — real respect for the Wesley Learns series; you got kids to investing without making it homework. Mine sits one rung below: before a kid invests, they have to survive a store. It teaches spending, ad to register. Feels complementary rather than competitive. It's a short read. The site: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Prince — real respect for the Wesley Learns books; you got kids to investing without it feeling like homework. Mine sits one rung below. Before a kid invests, he has to survive a store. Ad, aisle, comparison, coupon, register. Complementary rather than competitive, I think. Trade copies? More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L195" t="inlineStr"/>
@@ -10406,11 +10406,11 @@
         </is>
       </c>
       <c r="J196" t="n">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>Lynne: you give kids real money and real control, which is the practice version of what my book teaches in story form: compare, decide, pay, notice the tax. Would the families you work with use a read-along alongside the real thing? Background: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Lynne — you give kids real money and real control, which is the practice version of what mine teaches in story form: compare, decide, pay, notice the tax. Would the families you work with use a read-along alongside the real thing? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L196" t="inlineStr"/>
@@ -10456,11 +10456,11 @@
         </is>
       </c>
       <c r="J197" t="n">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
-          <t>Namrata, you teach parents to teach money to 5-15 year olds, which is exactly the handoff my book is designed for: the parent reads it aloud and the lesson does its own work. Would it fit the families in your academy? Details at https://clarencegetsabargain.com/ · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Namrata — you teach parents to teach money to 5-15 year olds, which is exactly the handoff mine is designed for. The parent reads it aloud and the lesson does its own work. Fit the families in your academy? More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L197" t="inlineStr"/>
@@ -10502,11 +10502,11 @@
         </is>
       </c>
       <c r="J198" t="n">
-        <v>344</v>
+        <v>299</v>
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>Michele — a CPA who writes for the public will appreciate this detail: my children's picture book teaches sales tax. A six-year-old pays it, notices, and gets an explanation. I don't think another kids' book does. Fit for anything you write? More at https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Michele — a CPA who writes for the public will appreciate this detail: my children's picture book teaches sales tax. A six-year-old pays it, notices, and gets an explanation. Fit anything you write? More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L198" t="inlineStr"/>
@@ -10548,11 +10548,11 @@
         </is>
       </c>
       <c r="J199" t="n">
-        <v>368</v>
+        <v>306</v>
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
-          <t>Ellen: consumer advocacy starts with knowing what you're being charged. My picture book teaches a six-year-old exactly that: compare prices, spot the markdown, and understand why the register total is higher than the sticker. Take a look or don't; either is fine. The site: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ellen — consumer advocacy starts with knowing what you're being charged. Mine teaches a six-year-old exactly that: compare prices, spot the markdown, understand why the register total climbed. Column material? More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L199" t="inlineStr"/>
@@ -10571,202 +10571,178 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="96" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="104" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>ITEM</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>DETAIL</t>
+          <t>RESULT</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sample flipbook</t>
+          <t>Voice source</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>On all 198. https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Your LinkedIn posts, the Crabby Guy book, the cover letter, and CLAUDE.md. Not the resume, which has your own kill-list words in it.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Website link</t>
+          <t>Em dashes</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>On all 198, routed by segment (see "Site link used" column).</t>
+          <t>On all 198. You said you use them without remorse, so my earlier reduction pass was reversed.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gatekeepers / districts</t>
+          <t>Rhetorical question then self-answer</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>educator-toolkit.html — the thing they would actually list or adopt.</t>
+          <t>Your signature move from the cover letter. Used throughout: "Did I verify that? Verified."</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Press</t>
+          <t>Legal register as comedy</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>press-kit.html — bios, art, fact sheet, interview questions.</t>
+          <t>"Matter of first impression," "a category of roughly one," deployed where it fits an attorney.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Librarians / academics</t>
+          <t>Precise dollars as punchline</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>book-facts.html — ISBN, LCCN, Lexile, concept list, glossary terms.</t>
+          <t>One cent for $300 shoes. 25 copies, $499.75. $19.99, PO and Net 30.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Credit unions / banks</t>
+          <t>Self-deprecating setup then flex</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>resources/grant-in-a-box.html — pre-written funding requests and CRA memo.</t>
+          <t>"I am an attorney who draws robots, not a researcher."</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Purchasing / procurement roles</t>
+          <t>Invite a fight</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>resources/procurement.html — specs, sole-source letter, PO and Net 30.</t>
+          <t>"Am I picking a fight the category does not want?" / "Real gap, or a convenient story?"</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Canonical URL</t>
+          <t>CLAUDE.md banned words</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Non-www. www.clarencegetsabargain.com 301-redirects; schema and sitemap still say www.</t>
+          <t>Clean. One hit is a job title (Leveraged Finance Reporter).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>No trimming</t>
+          <t>Kill-list "It is not X, it is Y"</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Messages are full length. InMail allows 1900 chars; max here is 545.</t>
+          <t>None.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CLAUDE.md word lists</t>
+          <t>Tired finance puns</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Clean. Only hit is "Leveraged Finance Reporter", a job title.</t>
+          <t>None.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kill-list constructions</t>
+          <t>Spoilers (Aisle Five, Wyze)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>None across all 198.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Spoilers (Aisle Five, Wyze)</t>
+          <t>Grammar pass</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>No flags.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Em-dash openers</t>
+          <t>Links</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>25%, across five greeting forms.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Ends on a question</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>38%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Grammar pass</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>396 checked. No flags.</t>
+          <t>Sample flipbook on all 198, plus a website page routed by segment.</t>
         </is>
       </c>
     </row>
